--- a/Excel Portfolio Projects/Emergency Services Review/Emergency Services Review Project.xlsx
+++ b/Excel Portfolio Projects/Emergency Services Review/Emergency Services Review Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a1ec44ccee5f08d5/Documents/Data Analysis/Portfolio/Excel Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="997" documentId="8_{88151A71-8DFA-4475-9035-398F879E8711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{433A7113-61FC-4808-A7F7-995CC0110388}"/>
+  <xr:revisionPtr revIDLastSave="1011" documentId="8_{88151A71-8DFA-4475-9035-398F879E8711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BE18E6F-A85F-4AC8-BBA9-D4A4B287A4DF}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-1790" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-1790" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Questions" sheetId="4" r:id="rId1"/>
@@ -348,10 +348,10 @@
       <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="165" formatCode="0.0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="0.0"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="0.0"/>
@@ -416,7 +416,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[UK_Public_Safety_Data_Project.xlsx]Raw Data!PivotTable4</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable4</c:name>
     <c:fmtId val="19"/>
   </c:pivotSource>
   <c:chart>
@@ -1469,7 +1469,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[UK_Public_Safety_Data_Project.xlsx]Raw Data!PivotTable5</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable5</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -2579,7 +2579,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[UK_Public_Safety_Data_Project.xlsx]Raw Data!PivotTable3</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable3</c:name>
     <c:fmtId val="7"/>
   </c:pivotSource>
   <c:chart>
@@ -4339,7 +4339,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[UK_Public_Safety_Data_Project.xlsx]Raw Data!PivotTable6</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable6</c:name>
     <c:fmtId val="9"/>
   </c:pivotSource>
   <c:chart>
@@ -4654,13 +4654,13 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
@@ -4711,13 +4711,13 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -6330,13 +6330,13 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
@@ -6526,13 +6526,13 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -6861,7 +6861,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[UK_Public_Safety_Data_Project.xlsx]Raw Data!PivotTable2</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable2</c:name>
     <c:fmtId val="17"/>
   </c:pivotSource>
   <c:chart>
@@ -7043,7 +7043,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="bg1"/>
                   </a:solidFill>
@@ -8625,7 +8625,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="bg1"/>
                     </a:solidFill>
@@ -10307,7 +10307,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[UK_Public_Safety_Data_Project.xlsx]Raw Data!PivotTable18</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable18</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -10850,7 +10850,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[UK_Public_Safety_Data_Project.xlsx]Raw Data!PivotTable19</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable19</c:name>
     <c:fmtId val="7"/>
   </c:pivotSource>
   <c:chart>
@@ -15977,7 +15977,7 @@
       <cdr:x>0.89742</cdr:x>
       <cdr:y>0.13203</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$29">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$28">
       <cdr:nvSpPr>
         <cdr:cNvPr id="18" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16098,7 +16098,7 @@
       <cdr:x>0.82085</cdr:x>
       <cdr:y>0.14201</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$28">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$27">
       <cdr:nvSpPr>
         <cdr:cNvPr id="33" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16219,7 +16219,7 @@
       <cdr:x>0.74243</cdr:x>
       <cdr:y>0.14502</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$27">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$26">
       <cdr:nvSpPr>
         <cdr:cNvPr id="34" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16340,7 +16340,7 @@
       <cdr:x>0.66648</cdr:x>
       <cdr:y>0.14202</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$26">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$25">
       <cdr:nvSpPr>
         <cdr:cNvPr id="35" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16461,7 +16461,7 @@
       <cdr:x>0.58639</cdr:x>
       <cdr:y>0.13769</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$25">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$24">
       <cdr:nvSpPr>
         <cdr:cNvPr id="38" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16582,7 +16582,7 @@
       <cdr:x>0.51225</cdr:x>
       <cdr:y>0.1261</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$24">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$23">
       <cdr:nvSpPr>
         <cdr:cNvPr id="37" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16703,7 +16703,7 @@
       <cdr:x>0.11512</cdr:x>
       <cdr:y>0.12038</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$19">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$18">
       <cdr:nvSpPr>
         <cdr:cNvPr id="39" name="TextBox 38">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16761,7 +16761,7 @@
       <cdr:x>0.19105</cdr:x>
       <cdr:y>0.13986</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$20">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$19">
       <cdr:nvSpPr>
         <cdr:cNvPr id="40" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16883,7 +16883,7 @@
       <cdr:x>0.26759</cdr:x>
       <cdr:y>0.13527</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$21">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$20">
       <cdr:nvSpPr>
         <cdr:cNvPr id="41" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -17004,7 +17004,7 @@
       <cdr:x>0.97584</cdr:x>
       <cdr:y>0.12036</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$30">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$29">
       <cdr:nvSpPr>
         <cdr:cNvPr id="42" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -17125,7 +17125,7 @@
       <cdr:x>0.34972</cdr:x>
       <cdr:y>0.13266</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$22">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$21">
       <cdr:nvSpPr>
         <cdr:cNvPr id="43" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -17246,7 +17246,7 @@
       <cdr:x>0.42752</cdr:x>
       <cdr:y>0.13043</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$Y$23">
+    <cdr:sp macro="" textlink="'Raw Data'!$X$22">
       <cdr:nvSpPr>
         <cdr:cNvPr id="44" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -25413,6 +25413,143 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E32690AA-A4BE-4EA8-B960-10C58710362E}" name="PivotTable18" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="T33:U47" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="7"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Public Satisfaction (%)" fld="10" subtotal="average" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="2">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5A0748F5-0DBB-4FCA-BA40-1AA3A02F43B4}" name="PivotTable2" cacheId="0" dataPosition="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
   <location ref="O1:R28" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -26532,7 +26669,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C55220A-B56C-4898-997C-ED31400853A5}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="O31:R40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="14">
@@ -26722,7 +26859,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70E5258A-CAC5-470F-A35B-D330CC354CE0}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="O43:R57" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="14">
@@ -26825,7 +26962,7 @@
     <dataField name="Average of Average Response Time (min)" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="7">
+    <format dxfId="8">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -26835,7 +26972,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -26844,7 +26981,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="6">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -26854,10 +26991,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="5">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="4">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -26866,7 +27003,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="3">
       <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -26998,7 +27135,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87152FF9-069B-4A5D-A601-9E3FB622E9C6}" name="PivotTable19" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="T49:U63" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
@@ -27093,7 +27230,7 @@
     <dataField name="Average of Public Satisfaction (%)" fld="10" subtotal="average" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="8">
+    <format dxfId="9">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -27118,143 +27255,6 @@
           </reference>
           <reference field="1" count="1" selected="0">
             <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E32690AA-A4BE-4EA8-B960-10C58710362E}" name="PivotTable18" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="T33:U47" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="7"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="0"/>
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Public Satisfaction (%)" fld="10" subtotal="average" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="9">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="10"/>
           </reference>
         </references>
       </pivotArea>
@@ -27628,7 +27628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y151"/>
+  <dimension ref="A1:X151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -28705,7 +28705,7 @@
         <v>0.93158153904268515</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -28765,7 +28765,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -28830,8 +28830,12 @@
       <c r="W18" t="s">
         <v>42</v>
       </c>
+      <c r="X18">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","East Midlands")</f>
+        <v>1031</v>
+      </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -28896,12 +28900,12 @@
       <c r="W19" s="13">
         <v>1031</v>
       </c>
-      <c r="Y19">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","East Midlands")</f>
-        <v>1031</v>
+      <c r="X19">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","East of England")</f>
+        <v>2067</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -28966,12 +28970,12 @@
       <c r="W20">
         <v>2067</v>
       </c>
-      <c r="Y20">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","East of England")</f>
-        <v>2067</v>
+      <c r="X20">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","London")</f>
+        <v>1060</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -29036,12 +29040,12 @@
       <c r="W21">
         <v>1060</v>
       </c>
-      <c r="Y21">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","London")</f>
-        <v>1060</v>
+      <c r="X21">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","North East")</f>
+        <v>1592</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -29106,12 +29110,12 @@
       <c r="W22">
         <v>1592</v>
       </c>
-      <c r="Y22">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","North East")</f>
-        <v>1592</v>
+      <c r="X22">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","North West")</f>
+        <v>2049</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -29176,12 +29180,12 @@
       <c r="W23">
         <v>2049</v>
       </c>
-      <c r="Y23">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","North West")</f>
-        <v>2049</v>
+      <c r="X23">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Northern Ireland")</f>
+        <v>857</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -29246,12 +29250,12 @@
       <c r="W24">
         <v>857</v>
       </c>
-      <c r="Y24">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Northern Ireland")</f>
-        <v>857</v>
+      <c r="X24">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Scotland")</f>
+        <v>1925</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -29316,12 +29320,12 @@
       <c r="W25">
         <v>1925</v>
       </c>
-      <c r="Y25">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Scotland")</f>
-        <v>1925</v>
+      <c r="X25">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","South East")</f>
+        <v>1480</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -29386,12 +29390,12 @@
       <c r="W26">
         <v>1480</v>
       </c>
-      <c r="Y26">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","South East")</f>
-        <v>1480</v>
+      <c r="X26">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","South West")</f>
+        <v>1382</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -29456,12 +29460,12 @@
       <c r="W27">
         <v>1382</v>
       </c>
-      <c r="Y27">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","South West")</f>
-        <v>1382</v>
+      <c r="X27">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Wales")</f>
+        <v>1796</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -29526,12 +29530,12 @@
       <c r="W28">
         <v>1796</v>
       </c>
-      <c r="Y28">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Wales")</f>
-        <v>1796</v>
+      <c r="X28">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","West Midlands")</f>
+        <v>1756</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -29584,12 +29588,12 @@
       <c r="W29">
         <v>1756</v>
       </c>
-      <c r="Y29">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","West Midlands")</f>
-        <v>1756</v>
+      <c r="X29">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Yorkshire and the Humber")</f>
+        <v>1234</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -29642,12 +29646,8 @@
       <c r="W30">
         <v>1234</v>
       </c>
-      <c r="Y30">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Yorkshire and the Humber")</f>
-        <v>1234</v>
-      </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -29707,7 +29707,7 @@
         <v>18229</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -35650,17 +35650,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f7ad296a-57ff-428c-b4cb-07edbf36982d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d161a28-3536-4ba6-9ad5-e5ce0dbbadc5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003B13CFFDAAE59C4CA678E7EE4E73178D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e05d12ad55831ca1d94ab0d6bf4c33ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f7ad296a-57ff-428c-b4cb-07edbf36982d" xmlns:ns3="2d161a28-3536-4ba6-9ad5-e5ce0dbbadc5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="accd58e9f676c36d920d788803336cd6" ns2:_="" ns3:_="">
     <xsd:import namespace="f7ad296a-57ff-428c-b4cb-07edbf36982d"/>
@@ -35855,6 +35844,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f7ad296a-57ff-428c-b4cb-07edbf36982d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d161a28-3536-4ba6-9ad5-e5ce0dbbadc5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1632C448-2796-4273-B186-9F60F8DD736F}">
   <ds:schemaRefs>
@@ -35864,23 +35864,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD253A9A-6DC7-4FA1-AF78-9A17C6B0F5FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="f7ad296a-57ff-428c-b4cb-07edbf36982d"/>
-    <ds:schemaRef ds:uri="2d161a28-3536-4ba6-9ad5-e5ce0dbbadc5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72BB855-D9E2-418E-8D59-E846EEFC1235}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -35897,4 +35880,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD253A9A-6DC7-4FA1-AF78-9A17C6B0F5FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="f7ad296a-57ff-428c-b4cb-07edbf36982d"/>
+    <ds:schemaRef ds:uri="2d161a28-3536-4ba6-9ad5-e5ce0dbbadc5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel Portfolio Projects/Emergency Services Review/Emergency Services Review Project.xlsx
+++ b/Excel Portfolio Projects/Emergency Services Review/Emergency Services Review Project.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a1ec44ccee5f08d5/Documents/Data Analysis/Portfolio/Excel Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1011" documentId="8_{88151A71-8DFA-4475-9035-398F879E8711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BE18E6F-A85F-4AC8-BBA9-D4A4B287A4DF}"/>
+  <xr:revisionPtr revIDLastSave="1034" documentId="8_{88151A71-8DFA-4475-9035-398F879E8711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B327160-BC58-4666-909C-3D015F07409F}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-1790" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Questions" sheetId="4" r:id="rId1"/>
-    <sheet name="Raw Data" sheetId="1" r:id="rId2"/>
-    <sheet name="Dashboard" sheetId="2" r:id="rId3"/>
-    <sheet name="Insights" sheetId="3" r:id="rId4"/>
+    <sheet name="Raw Data" sheetId="5" r:id="rId2"/>
+    <sheet name="Cleaned Data &amp; Pivot Table" sheetId="1" r:id="rId3"/>
+    <sheet name="Dashboard" sheetId="2" r:id="rId4"/>
+    <sheet name="Insights" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Department">#N/A</definedName>
@@ -24,14 +25,14 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="3" r:id="rId6"/>
+    <pivotCache cacheId="4" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId7"/>
         <x14:slicerCache r:id="rId8"/>
+        <x14:slicerCache r:id="rId9"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="55">
   <si>
     <t>Department</t>
   </si>
@@ -219,6 +220,9 @@
   <si>
     <t xml:space="preserve">% </t>
   </si>
+  <si>
+    <t>Grand Totals</t>
+  </si>
 </sst>
 </file>
 
@@ -281,7 +285,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -304,12 +308,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -332,6 +351,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -341,12 +366,6 @@
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="0.0"/>
     </dxf>
@@ -367,6 +386,12 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="0.0"/>
@@ -416,7 +441,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable4</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Cleaned Data &amp; Pivot Table!PivotTable4</c:name>
     <c:fmtId val="19"/>
   </c:pivotSource>
   <c:chart>
@@ -949,7 +974,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$U$1:$U$2</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$U$1:$U$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -994,7 +1019,7 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$T$3:$T$15</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$T$3:$T$15</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -1038,7 +1063,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$U$3:$U$15</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$U$3:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>"£"#,##0</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1092,7 +1117,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$V$1:$V$2</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$V$1:$V$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1143,7 +1168,7 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$T$3:$T$15</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$T$3:$T$15</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -1187,7 +1212,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$V$3:$V$15</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$V$3:$V$15</c:f>
               <c:numCache>
                 <c:formatCode>"£"#,##0</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1469,7 +1494,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable5</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Cleaned Data &amp; Pivot Table!PivotTable5</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -1945,7 +1970,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$P$43:$P$44</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$P$43:$P$44</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2057,7 +2082,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$O$45:$O$57</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$O$45:$O$57</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2101,7 +2126,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$P$45:$P$57</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$P$45:$P$57</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2155,7 +2180,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$Q$43:$Q$44</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$Q$43:$Q$44</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2273,7 +2298,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$O$45:$O$57</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$O$45:$O$57</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2317,7 +2342,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$Q$45:$Q$57</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$Q$45:$Q$57</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2579,7 +2604,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable3</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Cleaned Data &amp; Pivot Table!PivotTable3</c:name>
     <c:fmtId val="7"/>
   </c:pivotSource>
   <c:chart>
@@ -3726,7 +3751,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$P$31:$P$32</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$P$31:$P$32</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3865,7 +3890,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$O$33:$O$40</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$O$33:$O$40</c:f>
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
@@ -3894,7 +3919,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$P$33:$P$40</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$P$33:$P$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3933,7 +3958,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$Q$31:$Q$32</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$Q$31:$Q$32</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4048,7 +4073,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$O$33:$O$40</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$O$33:$O$40</c:f>
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
@@ -4077,7 +4102,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$Q$33:$Q$40</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$Q$33:$Q$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -4339,7 +4364,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable6</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Cleaned Data &amp; Pivot Table!PivotTable6</c:name>
     <c:fmtId val="9"/>
   </c:pivotSource>
   <c:chart>
@@ -4654,7 +4679,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
@@ -4711,7 +4736,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
@@ -6283,7 +6308,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$U$17:$U$18</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$U$17:$U$18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6330,7 +6355,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -6378,7 +6403,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$T$19:$T$31</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$T$19:$T$31</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -6422,7 +6447,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$U$19:$U$31</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$U$19:$U$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -6476,7 +6501,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$V$17:$V$18</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$V$17:$V$18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6526,7 +6551,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -6574,7 +6599,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$T$19:$T$31</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$T$19:$T$31</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -6618,7 +6643,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$V$19:$V$31</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$V$19:$V$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -6861,7 +6886,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable2</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Cleaned Data &amp; Pivot Table!PivotTable2</c:name>
     <c:fmtId val="17"/>
   </c:pivotSource>
   <c:chart>
@@ -8590,7 +8615,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$P$1</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$P$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8667,7 +8692,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Raw Data'!$O$2:$O$28</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$O$2:$O$28</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="24"/>
                 <c:lvl>
@@ -8757,7 +8782,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$P$2:$P$28</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$P$2:$P$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
@@ -8847,7 +8872,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$Q$1</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$Q$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8921,7 +8946,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Raw Data'!$O$2:$O$28</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$O$2:$O$28</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="24"/>
                 <c:lvl>
@@ -9011,7 +9036,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$Q$2:$Q$28</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$Q$2:$Q$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
@@ -9101,7 +9126,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$R$1</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$R$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9906,7 +9931,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Raw Data'!$O$2:$O$28</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$O$2:$O$28</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="24"/>
                 <c:lvl>
@@ -9996,7 +10021,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$R$2:$R$28</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$R$2:$R$28</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="24"/>
@@ -10307,7 +10332,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable18</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Cleaned Data &amp; Pivot Table!PivotTable18</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -10470,7 +10495,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$U$33</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$U$33</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10565,7 +10590,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Raw Data'!$T$34:$T$47</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$T$34:$T$47</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="12"/>
                 <c:lvl>
@@ -10616,7 +10641,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$U$34:$U$47</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$U$34:$U$47</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="12"/>
@@ -10850,7 +10875,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Emergency Services Review Project.xlsx]Raw Data!PivotTable19</c:name>
+    <c:name>[Emergency Services Review Project.xlsx]Cleaned Data &amp; Pivot Table!PivotTable19</c:name>
     <c:fmtId val="7"/>
   </c:pivotSource>
   <c:chart>
@@ -11098,7 +11123,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$U$49</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$U$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11191,7 +11216,7 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Raw Data'!$T$50:$T$63</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$T$50:$T$63</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="12"/>
                 <c:lvl>
@@ -11242,7 +11267,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$U$50:$U$63</c:f>
+              <c:f>'Cleaned Data &amp; Pivot Table'!$U$50:$U$63</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="12"/>
@@ -15977,7 +16002,7 @@
       <cdr:x>0.89742</cdr:x>
       <cdr:y>0.13203</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$28">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$29">
       <cdr:nvSpPr>
         <cdr:cNvPr id="18" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16098,7 +16123,7 @@
       <cdr:x>0.82085</cdr:x>
       <cdr:y>0.14201</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$27">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$28">
       <cdr:nvSpPr>
         <cdr:cNvPr id="33" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16219,7 +16244,7 @@
       <cdr:x>0.74243</cdr:x>
       <cdr:y>0.14502</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$26">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$27">
       <cdr:nvSpPr>
         <cdr:cNvPr id="34" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16340,7 +16365,7 @@
       <cdr:x>0.66648</cdr:x>
       <cdr:y>0.14202</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$25">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$26">
       <cdr:nvSpPr>
         <cdr:cNvPr id="35" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16461,7 +16486,7 @@
       <cdr:x>0.58639</cdr:x>
       <cdr:y>0.13769</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$24">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$25">
       <cdr:nvSpPr>
         <cdr:cNvPr id="38" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16582,7 +16607,7 @@
       <cdr:x>0.51225</cdr:x>
       <cdr:y>0.1261</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$23">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$24">
       <cdr:nvSpPr>
         <cdr:cNvPr id="37" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16703,7 +16728,7 @@
       <cdr:x>0.11512</cdr:x>
       <cdr:y>0.12038</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$18">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$19">
       <cdr:nvSpPr>
         <cdr:cNvPr id="39" name="TextBox 38">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16761,7 +16786,7 @@
       <cdr:x>0.19105</cdr:x>
       <cdr:y>0.13986</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$19">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$20">
       <cdr:nvSpPr>
         <cdr:cNvPr id="40" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -16883,7 +16908,7 @@
       <cdr:x>0.26759</cdr:x>
       <cdr:y>0.13527</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$20">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$21">
       <cdr:nvSpPr>
         <cdr:cNvPr id="41" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -17004,7 +17029,7 @@
       <cdr:x>0.97584</cdr:x>
       <cdr:y>0.12036</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$29">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$30">
       <cdr:nvSpPr>
         <cdr:cNvPr id="42" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -17125,7 +17150,7 @@
       <cdr:x>0.34972</cdr:x>
       <cdr:y>0.13266</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$21">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$22">
       <cdr:nvSpPr>
         <cdr:cNvPr id="43" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -17246,7 +17271,7 @@
       <cdr:x>0.42752</cdr:x>
       <cdr:y>0.13043</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'Raw Data'!$X$22">
+    <cdr:sp macro="" textlink="'Cleaned Data &amp; Pivot Table'!$X$23">
       <cdr:nvSpPr>
         <cdr:cNvPr id="44" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -20047,14 +20072,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Michael Owen" refreshedDate="46296.774786111113" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="150" xr:uid="{DF464AA4-20FA-4023-8741-7BD2382C91BC}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="B29" sheet="Raw Data"/>
+    <worksheetSource ref="B29" sheet="Cleaned Data &amp; Pivot Table"/>
   </cacheSource>
   <cacheFields count="14">
     <cacheField name="Department" numFmtId="0">
@@ -20320,7 +20341,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Michael Owen" refreshedDate="46299.097282175928" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="150" xr:uid="{DFD9CE5D-A63C-45D9-A96C-E218B1A5ECE9}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:M151" sheet="Raw Data"/>
+    <worksheetSource ref="A1:M151" sheet="Cleaned Data &amp; Pivot Table"/>
   </cacheSource>
   <cacheFields count="13">
     <cacheField name="Department" numFmtId="0">
@@ -24898,522 +24919,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{86147076-B354-420A-A76D-54C70BF26E8F}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
-  <location ref="T17:W31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="7"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Staff Count" fld="9" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="0">
-      <pivotArea field="1" grandCol="1" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="16">
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="15" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="16" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="17" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="18" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="19" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="20" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="21" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="22" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="23" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="24" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="25" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="1" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{267A9E03-2E5A-4865-8A1B-8469034CE9D2}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="29">
-  <location ref="T1:W15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="7"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Budget (£)" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="1">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="5">
-    <chartFormat chart="19" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E32690AA-A4BE-4EA8-B960-10C58710362E}" name="PivotTable18" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E32690AA-A4BE-4EA8-B960-10C58710362E}" name="PivotTable18" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="T33:U47" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField axis="axisRow" showAll="0">
@@ -25507,7 +25013,7 @@
     <dataField name="Average of Public Satisfaction (%)" fld="10" subtotal="average" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="2">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -25549,8 +25055,474 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C55220A-B56C-4898-997C-ED31400853A5}" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+  <location ref="O31:R40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="7"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="8">
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Incident Type" fld="3" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="7" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70E5258A-CAC5-470F-A35B-D330CC354CE0}" name="PivotTable5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+  <location ref="O43:R57" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="7"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Average Response Time (min)" fld="7" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="6">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="4">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="8">
+    <chartFormat chart="3" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5A0748F5-0DBB-4FCA-BA40-1AA3A02F43B4}" name="PivotTable2" cacheId="0" dataPosition="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5A0748F5-0DBB-4FCA-BA40-1AA3A02F43B4}" name="PivotTable2" cacheId="3" dataPosition="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="41">
   <location ref="O1:R28" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
@@ -26670,198 +26642,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C55220A-B56C-4898-997C-ED31400853A5}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
-  <location ref="O31:R40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="7"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="8">
-        <item x="4"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Incident Type" fld="3" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="7" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70E5258A-CAC5-470F-A35B-D330CC354CE0}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="O43:R57" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{86147076-B354-420A-A76D-54C70BF26E8F}" name="PivotTable6" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+  <location ref="T17:W31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
       <items count="3">
@@ -26892,8 +26674,333 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Staff Count" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="7">
+      <pivotArea field="1" grandCol="1" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="16">
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="16" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="17" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="18" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="19" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="20" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="25" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="1" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{267A9E03-2E5A-4865-8A1B-8469034CE9D2}" name="PivotTable4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="32">
+  <location ref="T1:W15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="7"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -26959,56 +27066,15 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of Average Response Time (min)" fld="7" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Budget (£)" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
-  <formats count="6">
+  <formats count="1">
     <format dxfId="8">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="7">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="6">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="5">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="4">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="3">
-      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="8">
-    <chartFormat chart="3" format="4" series="1">
+  <chartFormats count="5">
+    <chartFormat chart="19" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -27020,7 +27086,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="3" format="5" series="1">
+    <chartFormat chart="19" format="5" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -27032,7 +27098,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="3" format="6">
+    <chartFormat chart="19" format="6">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -27042,27 +27108,12 @@
             <x v="1"/>
           </reference>
           <reference field="1" count="1" selected="0">
-            <x v="2"/>
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="3" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="8">
+    <chartFormat chart="19" format="7">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -27072,42 +27123,12 @@
             <x v="1"/>
           </reference>
           <reference field="1" count="1" selected="0">
-            <x v="3"/>
+            <x v="6"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="3" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="11">
+    <chartFormat chart="19" format="8">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -27136,7 +27157,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87152FF9-069B-4A5D-A601-9E3FB622E9C6}" name="PivotTable19" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87152FF9-069B-4A5D-A601-9E3FB622E9C6}" name="PivotTable19" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="T49:U63" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField axis="axisRow" showAll="0">
@@ -27627,6 +27648,5772 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B34B1BA-5EBF-414B-A016-43C7EED2D063}">
+  <dimension ref="A1:L151"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>2020</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>152</v>
+      </c>
+      <c r="F2">
+        <v>152</v>
+      </c>
+      <c r="G2">
+        <v>11.7</v>
+      </c>
+      <c r="H2">
+        <v>1050645</v>
+      </c>
+      <c r="I2">
+        <v>128</v>
+      </c>
+      <c r="J2">
+        <v>98</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>2020</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>273</v>
+      </c>
+      <c r="F3">
+        <v>273</v>
+      </c>
+      <c r="G3">
+        <v>3.1</v>
+      </c>
+      <c r="H3">
+        <v>995635</v>
+      </c>
+      <c r="I3">
+        <v>112</v>
+      </c>
+      <c r="J3">
+        <v>93</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4">
+        <v>2024</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>708</v>
+      </c>
+      <c r="F4">
+        <v>541</v>
+      </c>
+      <c r="G4">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="H4">
+        <v>2051827</v>
+      </c>
+      <c r="I4">
+        <v>43</v>
+      </c>
+      <c r="J4">
+        <v>71</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>2020</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>716</v>
+      </c>
+      <c r="F5">
+        <v>97</v>
+      </c>
+      <c r="G5">
+        <v>7.9</v>
+      </c>
+      <c r="H5">
+        <v>1716124</v>
+      </c>
+      <c r="I5">
+        <v>88</v>
+      </c>
+      <c r="J5">
+        <v>75</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>2022</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>949</v>
+      </c>
+      <c r="F6">
+        <v>132</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>1235791</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>62</v>
+      </c>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7">
+        <v>2018</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>373</v>
+      </c>
+      <c r="F7">
+        <v>373</v>
+      </c>
+      <c r="G7">
+        <v>15.5</v>
+      </c>
+      <c r="H7">
+        <v>1913863</v>
+      </c>
+      <c r="I7">
+        <v>87</v>
+      </c>
+      <c r="J7">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <v>2024</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8">
+        <v>646</v>
+      </c>
+      <c r="F8">
+        <v>80</v>
+      </c>
+      <c r="G8">
+        <v>10.5</v>
+      </c>
+      <c r="H8">
+        <v>794512</v>
+      </c>
+      <c r="I8">
+        <v>41</v>
+      </c>
+      <c r="J8">
+        <v>97</v>
+      </c>
+      <c r="K8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9">
+        <v>2020</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9">
+        <v>654</v>
+      </c>
+      <c r="F9">
+        <v>654</v>
+      </c>
+      <c r="G9">
+        <v>11</v>
+      </c>
+      <c r="H9">
+        <v>598179</v>
+      </c>
+      <c r="I9">
+        <v>106</v>
+      </c>
+      <c r="J9">
+        <v>98</v>
+      </c>
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10">
+        <v>2024</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>583</v>
+      </c>
+      <c r="F10">
+        <v>465</v>
+      </c>
+      <c r="G10">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="H10">
+        <v>1784103</v>
+      </c>
+      <c r="I10">
+        <v>46</v>
+      </c>
+      <c r="J10">
+        <v>91</v>
+      </c>
+      <c r="K10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>2024</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11">
+        <v>787</v>
+      </c>
+      <c r="F11">
+        <v>295</v>
+      </c>
+      <c r="G11">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="H11">
+        <v>638298</v>
+      </c>
+      <c r="I11">
+        <v>198</v>
+      </c>
+      <c r="J11">
+        <v>77</v>
+      </c>
+      <c r="K11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12">
+        <v>2020</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12">
+        <v>272</v>
+      </c>
+      <c r="F12">
+        <v>272</v>
+      </c>
+      <c r="G12">
+        <v>7.2</v>
+      </c>
+      <c r="H12">
+        <v>914553</v>
+      </c>
+      <c r="I12">
+        <v>148</v>
+      </c>
+      <c r="J12">
+        <v>94</v>
+      </c>
+      <c r="K12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13">
+        <v>2023</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>503</v>
+      </c>
+      <c r="F13">
+        <v>503</v>
+      </c>
+      <c r="G13">
+        <v>6.3</v>
+      </c>
+      <c r="H13">
+        <v>1894138</v>
+      </c>
+      <c r="I13">
+        <v>154</v>
+      </c>
+      <c r="J13">
+        <v>64</v>
+      </c>
+      <c r="K13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14">
+        <v>2020</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14">
+        <v>896</v>
+      </c>
+      <c r="F14">
+        <v>424</v>
+      </c>
+      <c r="G14">
+        <v>17.2</v>
+      </c>
+      <c r="H14">
+        <v>646940</v>
+      </c>
+      <c r="I14">
+        <v>61</v>
+      </c>
+      <c r="J14">
+        <v>69</v>
+      </c>
+      <c r="K14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15">
+        <v>2021</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15">
+        <v>612</v>
+      </c>
+      <c r="F15">
+        <v>104</v>
+      </c>
+      <c r="G15">
+        <v>16.3</v>
+      </c>
+      <c r="H15">
+        <v>1953890</v>
+      </c>
+      <c r="I15">
+        <v>40</v>
+      </c>
+      <c r="J15">
+        <v>67</v>
+      </c>
+      <c r="K15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16">
+        <v>2019</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16">
+        <v>378</v>
+      </c>
+      <c r="F16">
+        <v>151</v>
+      </c>
+      <c r="G16">
+        <v>11.5</v>
+      </c>
+      <c r="H16">
+        <v>2343950</v>
+      </c>
+      <c r="I16">
+        <v>129</v>
+      </c>
+      <c r="J16">
+        <v>94</v>
+      </c>
+      <c r="K16" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17">
+        <v>2020</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17">
+        <v>819</v>
+      </c>
+      <c r="F17">
+        <v>145</v>
+      </c>
+      <c r="G17">
+        <v>17.7</v>
+      </c>
+      <c r="H17">
+        <v>942193</v>
+      </c>
+      <c r="I17">
+        <v>94</v>
+      </c>
+      <c r="J17">
+        <v>64</v>
+      </c>
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18">
+        <v>2022</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18">
+        <v>343</v>
+      </c>
+      <c r="F18">
+        <v>228</v>
+      </c>
+      <c r="G18">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="H18">
+        <v>1987198</v>
+      </c>
+      <c r="I18">
+        <v>187</v>
+      </c>
+      <c r="J18">
+        <v>93</v>
+      </c>
+      <c r="K18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19">
+        <v>2021</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19">
+        <v>203</v>
+      </c>
+      <c r="F19">
+        <v>153</v>
+      </c>
+      <c r="G19">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="H19">
+        <v>2496711</v>
+      </c>
+      <c r="I19">
+        <v>96</v>
+      </c>
+      <c r="J19">
+        <v>68</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20">
+        <v>2023</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20">
+        <v>961</v>
+      </c>
+      <c r="F20">
+        <v>239</v>
+      </c>
+      <c r="G20">
+        <v>12</v>
+      </c>
+      <c r="H20">
+        <v>577536</v>
+      </c>
+      <c r="I20">
+        <v>142</v>
+      </c>
+      <c r="J20">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s">
+        <v>15</v>
+      </c>
+      <c r="L20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21">
+        <v>2018</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21">
+        <v>355</v>
+      </c>
+      <c r="F21">
+        <v>355</v>
+      </c>
+      <c r="G21">
+        <v>17.3</v>
+      </c>
+      <c r="H21">
+        <v>1457685</v>
+      </c>
+      <c r="I21">
+        <v>85</v>
+      </c>
+      <c r="J21">
+        <v>82</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22">
+        <v>2024</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22">
+        <v>304</v>
+      </c>
+      <c r="F22">
+        <v>304</v>
+      </c>
+      <c r="G22">
+        <v>12.1</v>
+      </c>
+      <c r="H22">
+        <v>2083742</v>
+      </c>
+      <c r="I22">
+        <v>81</v>
+      </c>
+      <c r="J22">
+        <v>81</v>
+      </c>
+      <c r="K22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23">
+        <v>2022</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23">
+        <v>368</v>
+      </c>
+      <c r="F23">
+        <v>368</v>
+      </c>
+      <c r="G23">
+        <v>11.9</v>
+      </c>
+      <c r="H23">
+        <v>1373361</v>
+      </c>
+      <c r="I23">
+        <v>89</v>
+      </c>
+      <c r="J23">
+        <v>78</v>
+      </c>
+      <c r="K23" t="s">
+        <v>15</v>
+      </c>
+      <c r="L23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24">
+        <v>2018</v>
+      </c>
+      <c r="D24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24">
+        <v>278</v>
+      </c>
+      <c r="F24">
+        <v>105</v>
+      </c>
+      <c r="G24">
+        <v>10.5</v>
+      </c>
+      <c r="H24">
+        <v>2043881</v>
+      </c>
+      <c r="I24">
+        <v>96</v>
+      </c>
+      <c r="J24">
+        <v>67</v>
+      </c>
+      <c r="K24" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25">
+        <v>2022</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25">
+        <v>294</v>
+      </c>
+      <c r="F25">
+        <v>294</v>
+      </c>
+      <c r="G25">
+        <v>7.3</v>
+      </c>
+      <c r="H25">
+        <v>1723430</v>
+      </c>
+      <c r="I25">
+        <v>191</v>
+      </c>
+      <c r="J25">
+        <v>65</v>
+      </c>
+      <c r="K25" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26">
+        <v>2024</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26">
+        <v>193</v>
+      </c>
+      <c r="F26">
+        <v>193</v>
+      </c>
+      <c r="G26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="H26">
+        <v>1684448</v>
+      </c>
+      <c r="I26">
+        <v>47</v>
+      </c>
+      <c r="J26">
+        <v>87</v>
+      </c>
+      <c r="K26" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27">
+        <v>2023</v>
+      </c>
+      <c r="D27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27">
+        <v>229</v>
+      </c>
+      <c r="F27">
+        <v>229</v>
+      </c>
+      <c r="G27">
+        <v>9</v>
+      </c>
+      <c r="H27">
+        <v>670643</v>
+      </c>
+      <c r="I27">
+        <v>192</v>
+      </c>
+      <c r="J27">
+        <v>81</v>
+      </c>
+      <c r="K27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28">
+        <v>2021</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28">
+        <v>338</v>
+      </c>
+      <c r="F28">
+        <v>109</v>
+      </c>
+      <c r="G28">
+        <v>3.3</v>
+      </c>
+      <c r="H28">
+        <v>753279</v>
+      </c>
+      <c r="I28">
+        <v>76</v>
+      </c>
+      <c r="J28">
+        <v>78</v>
+      </c>
+      <c r="K28" t="s">
+        <v>19</v>
+      </c>
+      <c r="L28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29">
+        <v>2022</v>
+      </c>
+      <c r="D29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29">
+        <v>754</v>
+      </c>
+      <c r="F29">
+        <v>86</v>
+      </c>
+      <c r="G29">
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <v>1150408</v>
+      </c>
+      <c r="I29">
+        <v>53</v>
+      </c>
+      <c r="J29">
+        <v>81</v>
+      </c>
+      <c r="K29" t="s">
+        <v>27</v>
+      </c>
+      <c r="L29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30">
+        <v>2021</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30">
+        <v>624</v>
+      </c>
+      <c r="F30">
+        <v>89</v>
+      </c>
+      <c r="G30">
+        <v>3.8</v>
+      </c>
+      <c r="H30">
+        <v>1193310</v>
+      </c>
+      <c r="I30">
+        <v>103</v>
+      </c>
+      <c r="J30">
+        <v>98</v>
+      </c>
+      <c r="K30" t="s">
+        <v>19</v>
+      </c>
+      <c r="L30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31">
+        <v>2018</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31">
+        <v>270</v>
+      </c>
+      <c r="F31">
+        <v>270</v>
+      </c>
+      <c r="G31">
+        <v>19.3</v>
+      </c>
+      <c r="H31">
+        <v>1135651</v>
+      </c>
+      <c r="I31">
+        <v>154</v>
+      </c>
+      <c r="J31">
+        <v>75</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32">
+        <v>2022</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32">
+        <v>421</v>
+      </c>
+      <c r="F32">
+        <v>325</v>
+      </c>
+      <c r="G32">
+        <v>13.4</v>
+      </c>
+      <c r="H32">
+        <v>2163263</v>
+      </c>
+      <c r="I32">
+        <v>124</v>
+      </c>
+      <c r="J32">
+        <v>91</v>
+      </c>
+      <c r="K32" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33">
+        <v>2024</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33">
+        <v>269</v>
+      </c>
+      <c r="F33">
+        <v>224</v>
+      </c>
+      <c r="G33">
+        <v>8.9</v>
+      </c>
+      <c r="H33">
+        <v>1810091</v>
+      </c>
+      <c r="I33">
+        <v>89</v>
+      </c>
+      <c r="J33">
+        <v>82</v>
+      </c>
+      <c r="K33" t="s">
+        <v>27</v>
+      </c>
+      <c r="L33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34">
+        <v>2020</v>
+      </c>
+      <c r="D34" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34">
+        <v>926</v>
+      </c>
+      <c r="F34">
+        <v>437</v>
+      </c>
+      <c r="G34">
+        <v>4.3</v>
+      </c>
+      <c r="H34">
+        <v>636733</v>
+      </c>
+      <c r="I34">
+        <v>152</v>
+      </c>
+      <c r="J34">
+        <v>98</v>
+      </c>
+      <c r="K34" t="s">
+        <v>19</v>
+      </c>
+      <c r="L34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35">
+        <v>2021</v>
+      </c>
+      <c r="D35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35">
+        <v>208</v>
+      </c>
+      <c r="F35">
+        <v>208</v>
+      </c>
+      <c r="G35">
+        <v>6.8</v>
+      </c>
+      <c r="H35">
+        <v>739258</v>
+      </c>
+      <c r="I35">
+        <v>107</v>
+      </c>
+      <c r="J35">
+        <v>72</v>
+      </c>
+      <c r="K35" t="s">
+        <v>27</v>
+      </c>
+      <c r="L35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36">
+        <v>2022</v>
+      </c>
+      <c r="D36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36">
+        <v>855</v>
+      </c>
+      <c r="F36">
+        <v>649</v>
+      </c>
+      <c r="G36">
+        <v>17.3</v>
+      </c>
+      <c r="H36">
+        <v>1813579</v>
+      </c>
+      <c r="I36">
+        <v>194</v>
+      </c>
+      <c r="J36">
+        <v>65</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37">
+        <v>2024</v>
+      </c>
+      <c r="D37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37">
+        <v>780</v>
+      </c>
+      <c r="F37">
+        <v>780</v>
+      </c>
+      <c r="G37">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="H37">
+        <v>1703128</v>
+      </c>
+      <c r="I37">
+        <v>193</v>
+      </c>
+      <c r="J37">
+        <v>70</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38">
+        <v>2023</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38">
+        <v>771</v>
+      </c>
+      <c r="F38">
+        <v>771</v>
+      </c>
+      <c r="G38">
+        <v>6.3</v>
+      </c>
+      <c r="H38">
+        <v>979153</v>
+      </c>
+      <c r="I38">
+        <v>132</v>
+      </c>
+      <c r="J38">
+        <v>66</v>
+      </c>
+      <c r="K38" t="s">
+        <v>27</v>
+      </c>
+      <c r="L38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39">
+        <v>2018</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39">
+        <v>107</v>
+      </c>
+      <c r="F39">
+        <v>53</v>
+      </c>
+      <c r="G39">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="H39">
+        <v>1085385</v>
+      </c>
+      <c r="I39">
+        <v>170</v>
+      </c>
+      <c r="J39">
+        <v>94</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40">
+        <v>2020</v>
+      </c>
+      <c r="D40" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40">
+        <v>151</v>
+      </c>
+      <c r="F40">
+        <v>151</v>
+      </c>
+      <c r="G40">
+        <v>19</v>
+      </c>
+      <c r="H40">
+        <v>993438</v>
+      </c>
+      <c r="I40">
+        <v>178</v>
+      </c>
+      <c r="J40">
+        <v>88</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41">
+        <v>2021</v>
+      </c>
+      <c r="D41" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41">
+        <v>845</v>
+      </c>
+      <c r="F41">
+        <v>691</v>
+      </c>
+      <c r="G41">
+        <v>15</v>
+      </c>
+      <c r="H41">
+        <v>1454509</v>
+      </c>
+      <c r="I41">
+        <v>109</v>
+      </c>
+      <c r="J41">
+        <v>70</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42">
+        <v>2021</v>
+      </c>
+      <c r="D42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42">
+        <v>850</v>
+      </c>
+      <c r="F42">
+        <v>850</v>
+      </c>
+      <c r="G42">
+        <v>3.1</v>
+      </c>
+      <c r="H42">
+        <v>861650</v>
+      </c>
+      <c r="I42">
+        <v>123</v>
+      </c>
+      <c r="J42">
+        <v>78</v>
+      </c>
+      <c r="K42" t="s">
+        <v>19</v>
+      </c>
+      <c r="L42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43">
+        <v>2021</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43">
+        <v>966</v>
+      </c>
+      <c r="F43">
+        <v>686</v>
+      </c>
+      <c r="G43">
+        <v>17.7</v>
+      </c>
+      <c r="H43">
+        <v>858402</v>
+      </c>
+      <c r="I43">
+        <v>94</v>
+      </c>
+      <c r="J43">
+        <v>64</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44">
+        <v>2022</v>
+      </c>
+      <c r="D44" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44">
+        <v>879</v>
+      </c>
+      <c r="F44">
+        <v>663</v>
+      </c>
+      <c r="G44">
+        <v>4.3</v>
+      </c>
+      <c r="H44">
+        <v>1473688</v>
+      </c>
+      <c r="I44">
+        <v>168</v>
+      </c>
+      <c r="J44">
+        <v>86</v>
+      </c>
+      <c r="K44" t="s">
+        <v>19</v>
+      </c>
+      <c r="L44" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45">
+        <v>2022</v>
+      </c>
+      <c r="D45" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45">
+        <v>662</v>
+      </c>
+      <c r="F45">
+        <v>166</v>
+      </c>
+      <c r="G45">
+        <v>14.8</v>
+      </c>
+      <c r="H45">
+        <v>906513</v>
+      </c>
+      <c r="I45">
+        <v>129</v>
+      </c>
+      <c r="J45">
+        <v>75</v>
+      </c>
+      <c r="K45" t="s">
+        <v>15</v>
+      </c>
+      <c r="L45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46">
+        <v>2020</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46">
+        <v>624</v>
+      </c>
+      <c r="F46">
+        <v>419</v>
+      </c>
+      <c r="G46">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H46">
+        <v>2053334</v>
+      </c>
+      <c r="I46">
+        <v>78</v>
+      </c>
+      <c r="J46">
+        <v>93</v>
+      </c>
+      <c r="K46" t="s">
+        <v>27</v>
+      </c>
+      <c r="L46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47">
+        <v>2022</v>
+      </c>
+      <c r="D47" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47">
+        <v>542</v>
+      </c>
+      <c r="F47">
+        <v>173</v>
+      </c>
+      <c r="G47">
+        <v>15</v>
+      </c>
+      <c r="H47">
+        <v>1901077</v>
+      </c>
+      <c r="I47">
+        <v>175</v>
+      </c>
+      <c r="J47">
+        <v>85</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48">
+        <v>2021</v>
+      </c>
+      <c r="D48" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48">
+        <v>676</v>
+      </c>
+      <c r="F48">
+        <v>676</v>
+      </c>
+      <c r="G48">
+        <v>12.7</v>
+      </c>
+      <c r="H48">
+        <v>1405511</v>
+      </c>
+      <c r="I48">
+        <v>146</v>
+      </c>
+      <c r="J48">
+        <v>69</v>
+      </c>
+      <c r="K48" t="s">
+        <v>15</v>
+      </c>
+      <c r="L48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49">
+        <v>2023</v>
+      </c>
+      <c r="D49" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49">
+        <v>114</v>
+      </c>
+      <c r="F49">
+        <v>114</v>
+      </c>
+      <c r="G49">
+        <v>12.2</v>
+      </c>
+      <c r="H49">
+        <v>1558371</v>
+      </c>
+      <c r="I49">
+        <v>167</v>
+      </c>
+      <c r="J49">
+        <v>86</v>
+      </c>
+      <c r="K49" t="s">
+        <v>15</v>
+      </c>
+      <c r="L49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50">
+        <v>2022</v>
+      </c>
+      <c r="D50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50">
+        <v>567</v>
+      </c>
+      <c r="F50">
+        <v>303</v>
+      </c>
+      <c r="G50">
+        <v>4.2</v>
+      </c>
+      <c r="H50">
+        <v>1001580</v>
+      </c>
+      <c r="I50">
+        <v>179</v>
+      </c>
+      <c r="J50">
+        <v>83</v>
+      </c>
+      <c r="K50" t="s">
+        <v>19</v>
+      </c>
+      <c r="L50" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51">
+        <v>2023</v>
+      </c>
+      <c r="D51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51">
+        <v>106</v>
+      </c>
+      <c r="F51">
+        <v>106</v>
+      </c>
+      <c r="G51">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="H51">
+        <v>1962609</v>
+      </c>
+      <c r="I51">
+        <v>181</v>
+      </c>
+      <c r="J51">
+        <v>86</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52">
+        <v>2018</v>
+      </c>
+      <c r="D52" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52">
+        <v>284</v>
+      </c>
+      <c r="F52">
+        <v>284</v>
+      </c>
+      <c r="G52">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H52">
+        <v>1146606</v>
+      </c>
+      <c r="I52">
+        <v>81</v>
+      </c>
+      <c r="J52">
+        <v>97</v>
+      </c>
+      <c r="K52" t="s">
+        <v>27</v>
+      </c>
+      <c r="L52" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53">
+        <v>2020</v>
+      </c>
+      <c r="D53" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53">
+        <v>798</v>
+      </c>
+      <c r="F53">
+        <v>702</v>
+      </c>
+      <c r="G53">
+        <v>3.1</v>
+      </c>
+      <c r="H53">
+        <v>1730929</v>
+      </c>
+      <c r="I53">
+        <v>123</v>
+      </c>
+      <c r="J53">
+        <v>71</v>
+      </c>
+      <c r="K53" t="s">
+        <v>19</v>
+      </c>
+      <c r="L53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54">
+        <v>2024</v>
+      </c>
+      <c r="D54" t="s">
+        <v>32</v>
+      </c>
+      <c r="E54">
+        <v>869</v>
+      </c>
+      <c r="F54">
+        <v>466</v>
+      </c>
+      <c r="G54">
+        <v>11.5</v>
+      </c>
+      <c r="H54">
+        <v>1511149</v>
+      </c>
+      <c r="I54">
+        <v>143</v>
+      </c>
+      <c r="J54">
+        <v>62</v>
+      </c>
+      <c r="K54" t="s">
+        <v>15</v>
+      </c>
+      <c r="L54" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55">
+        <v>2022</v>
+      </c>
+      <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55">
+        <v>822</v>
+      </c>
+      <c r="F55">
+        <v>200</v>
+      </c>
+      <c r="G55">
+        <v>5.2</v>
+      </c>
+      <c r="H55">
+        <v>1814415</v>
+      </c>
+      <c r="I55">
+        <v>38</v>
+      </c>
+      <c r="J55">
+        <v>82</v>
+      </c>
+      <c r="K55" t="s">
+        <v>27</v>
+      </c>
+      <c r="L55" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56">
+        <v>2018</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56">
+        <v>812</v>
+      </c>
+      <c r="F56">
+        <v>781</v>
+      </c>
+      <c r="G56">
+        <v>19.3</v>
+      </c>
+      <c r="H56">
+        <v>2472849</v>
+      </c>
+      <c r="I56">
+        <v>166</v>
+      </c>
+      <c r="J56">
+        <v>81</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57">
+        <v>2023</v>
+      </c>
+      <c r="D57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57">
+        <v>966</v>
+      </c>
+      <c r="F57">
+        <v>369</v>
+      </c>
+      <c r="G57">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="H57">
+        <v>810382</v>
+      </c>
+      <c r="I57">
+        <v>94</v>
+      </c>
+      <c r="J57">
+        <v>70</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" t="s">
+        <v>36</v>
+      </c>
+      <c r="C58">
+        <v>2020</v>
+      </c>
+      <c r="D58" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58">
+        <v>177</v>
+      </c>
+      <c r="F58">
+        <v>81</v>
+      </c>
+      <c r="G58">
+        <v>9</v>
+      </c>
+      <c r="H58">
+        <v>1814883</v>
+      </c>
+      <c r="I58">
+        <v>168</v>
+      </c>
+      <c r="J58">
+        <v>88</v>
+      </c>
+      <c r="K58" t="s">
+        <v>27</v>
+      </c>
+      <c r="L58" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59">
+        <v>2021</v>
+      </c>
+      <c r="D59" t="s">
+        <v>32</v>
+      </c>
+      <c r="E59">
+        <v>551</v>
+      </c>
+      <c r="F59">
+        <v>551</v>
+      </c>
+      <c r="G59">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="H59">
+        <v>1280791</v>
+      </c>
+      <c r="I59">
+        <v>31</v>
+      </c>
+      <c r="J59">
+        <v>99</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60">
+        <v>2019</v>
+      </c>
+      <c r="D60" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60">
+        <v>844</v>
+      </c>
+      <c r="F60">
+        <v>655</v>
+      </c>
+      <c r="G60">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="H60">
+        <v>731974</v>
+      </c>
+      <c r="I60">
+        <v>53</v>
+      </c>
+      <c r="J60">
+        <v>63</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61">
+        <v>2020</v>
+      </c>
+      <c r="D61" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61">
+        <v>964</v>
+      </c>
+      <c r="F61">
+        <v>759</v>
+      </c>
+      <c r="G61">
+        <v>3</v>
+      </c>
+      <c r="H61">
+        <v>1891357</v>
+      </c>
+      <c r="I61">
+        <v>79</v>
+      </c>
+      <c r="J61">
+        <v>76</v>
+      </c>
+      <c r="K61" t="s">
+        <v>19</v>
+      </c>
+      <c r="L61" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>36</v>
+      </c>
+      <c r="C62">
+        <v>2021</v>
+      </c>
+      <c r="D62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E62">
+        <v>799</v>
+      </c>
+      <c r="F62">
+        <v>608</v>
+      </c>
+      <c r="G62">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="H62">
+        <v>1970495</v>
+      </c>
+      <c r="I62">
+        <v>199</v>
+      </c>
+      <c r="J62">
+        <v>87</v>
+      </c>
+      <c r="K62" t="s">
+        <v>27</v>
+      </c>
+      <c r="L62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63">
+        <v>2018</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63">
+        <v>550</v>
+      </c>
+      <c r="F63">
+        <v>550</v>
+      </c>
+      <c r="G63">
+        <v>7.2</v>
+      </c>
+      <c r="H63">
+        <v>853184</v>
+      </c>
+      <c r="I63">
+        <v>159</v>
+      </c>
+      <c r="J63">
+        <v>67</v>
+      </c>
+      <c r="K63" t="s">
+        <v>27</v>
+      </c>
+      <c r="L63" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64">
+        <v>2020</v>
+      </c>
+      <c r="D64" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64">
+        <v>355</v>
+      </c>
+      <c r="F64">
+        <v>221</v>
+      </c>
+      <c r="G64">
+        <v>10</v>
+      </c>
+      <c r="H64">
+        <v>2213736</v>
+      </c>
+      <c r="I64">
+        <v>168</v>
+      </c>
+      <c r="J64">
+        <v>70</v>
+      </c>
+      <c r="K64" t="s">
+        <v>15</v>
+      </c>
+      <c r="L64" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>33</v>
+      </c>
+      <c r="C65">
+        <v>2024</v>
+      </c>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65">
+        <v>961</v>
+      </c>
+      <c r="F65">
+        <v>265</v>
+      </c>
+      <c r="G65">
+        <v>6</v>
+      </c>
+      <c r="H65">
+        <v>2353760</v>
+      </c>
+      <c r="I65">
+        <v>90</v>
+      </c>
+      <c r="J65">
+        <v>94</v>
+      </c>
+      <c r="K65" t="s">
+        <v>27</v>
+      </c>
+      <c r="L65" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66">
+        <v>2022</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66">
+        <v>216</v>
+      </c>
+      <c r="F66">
+        <v>216</v>
+      </c>
+      <c r="G66">
+        <v>16.2</v>
+      </c>
+      <c r="H66">
+        <v>560724</v>
+      </c>
+      <c r="I66">
+        <v>165</v>
+      </c>
+      <c r="J66">
+        <v>72</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67">
+        <v>2022</v>
+      </c>
+      <c r="D67" t="s">
+        <v>34</v>
+      </c>
+      <c r="E67">
+        <v>194</v>
+      </c>
+      <c r="F67">
+        <v>194</v>
+      </c>
+      <c r="G67">
+        <v>13</v>
+      </c>
+      <c r="H67">
+        <v>1176212</v>
+      </c>
+      <c r="I67">
+        <v>177</v>
+      </c>
+      <c r="J67">
+        <v>99</v>
+      </c>
+      <c r="K67" t="s">
+        <v>15</v>
+      </c>
+      <c r="L67" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68">
+        <v>2019</v>
+      </c>
+      <c r="D68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E68">
+        <v>673</v>
+      </c>
+      <c r="F68">
+        <v>72</v>
+      </c>
+      <c r="G68">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="H68">
+        <v>2121182</v>
+      </c>
+      <c r="I68">
+        <v>41</v>
+      </c>
+      <c r="J68">
+        <v>70</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69">
+        <v>2020</v>
+      </c>
+      <c r="D69" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69">
+        <v>297</v>
+      </c>
+      <c r="F69">
+        <v>297</v>
+      </c>
+      <c r="G69">
+        <v>5</v>
+      </c>
+      <c r="H69">
+        <v>1665783</v>
+      </c>
+      <c r="I69">
+        <v>102</v>
+      </c>
+      <c r="J69">
+        <v>80</v>
+      </c>
+      <c r="K69" t="s">
+        <v>27</v>
+      </c>
+      <c r="L69" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" t="s">
+        <v>36</v>
+      </c>
+      <c r="C70">
+        <v>2022</v>
+      </c>
+      <c r="D70" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70">
+        <v>709</v>
+      </c>
+      <c r="F70">
+        <v>371</v>
+      </c>
+      <c r="G70">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="H70">
+        <v>1679416</v>
+      </c>
+      <c r="I70">
+        <v>46</v>
+      </c>
+      <c r="J70">
+        <v>99</v>
+      </c>
+      <c r="K70" t="s">
+        <v>27</v>
+      </c>
+      <c r="L70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>39</v>
+      </c>
+      <c r="C71">
+        <v>2018</v>
+      </c>
+      <c r="D71" t="s">
+        <v>34</v>
+      </c>
+      <c r="E71">
+        <v>262</v>
+      </c>
+      <c r="F71">
+        <v>262</v>
+      </c>
+      <c r="G71">
+        <v>6.9</v>
+      </c>
+      <c r="H71">
+        <v>1498822</v>
+      </c>
+      <c r="I71">
+        <v>113</v>
+      </c>
+      <c r="J71">
+        <v>97</v>
+      </c>
+      <c r="K71" t="s">
+        <v>27</v>
+      </c>
+      <c r="L71" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72">
+        <v>2018</v>
+      </c>
+      <c r="D72" t="s">
+        <v>34</v>
+      </c>
+      <c r="E72">
+        <v>294</v>
+      </c>
+      <c r="F72">
+        <v>294</v>
+      </c>
+      <c r="G72">
+        <v>9.4</v>
+      </c>
+      <c r="H72">
+        <v>801207</v>
+      </c>
+      <c r="I72">
+        <v>189</v>
+      </c>
+      <c r="J72">
+        <v>76</v>
+      </c>
+      <c r="K72" t="s">
+        <v>27</v>
+      </c>
+      <c r="L72" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>12</v>
+      </c>
+      <c r="B73" t="s">
+        <v>40</v>
+      </c>
+      <c r="C73">
+        <v>2023</v>
+      </c>
+      <c r="D73" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73">
+        <v>141</v>
+      </c>
+      <c r="F73">
+        <v>141</v>
+      </c>
+      <c r="G73">
+        <v>13.5</v>
+      </c>
+      <c r="H73">
+        <v>2485898</v>
+      </c>
+      <c r="I73">
+        <v>63</v>
+      </c>
+      <c r="J73">
+        <v>94</v>
+      </c>
+      <c r="K73" t="s">
+        <v>15</v>
+      </c>
+      <c r="L73" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74">
+        <v>2022</v>
+      </c>
+      <c r="D74" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74">
+        <v>124</v>
+      </c>
+      <c r="F74">
+        <v>79</v>
+      </c>
+      <c r="G74">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="H74">
+        <v>772022</v>
+      </c>
+      <c r="I74">
+        <v>198</v>
+      </c>
+      <c r="J74">
+        <v>98</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" t="s">
+        <v>21</v>
+      </c>
+      <c r="C75">
+        <v>2021</v>
+      </c>
+      <c r="D75" t="s">
+        <v>32</v>
+      </c>
+      <c r="E75">
+        <v>407</v>
+      </c>
+      <c r="F75">
+        <v>407</v>
+      </c>
+      <c r="G75">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H75">
+        <v>2024904</v>
+      </c>
+      <c r="I75">
+        <v>176</v>
+      </c>
+      <c r="J75">
+        <v>81</v>
+      </c>
+      <c r="K75" t="s">
+        <v>27</v>
+      </c>
+      <c r="L75" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76">
+        <v>2018</v>
+      </c>
+      <c r="D76" t="s">
+        <v>34</v>
+      </c>
+      <c r="E76">
+        <v>939</v>
+      </c>
+      <c r="F76">
+        <v>751</v>
+      </c>
+      <c r="G76">
+        <v>9.1</v>
+      </c>
+      <c r="H76">
+        <v>2395283</v>
+      </c>
+      <c r="I76">
+        <v>98</v>
+      </c>
+      <c r="J76">
+        <v>80</v>
+      </c>
+      <c r="K76" t="s">
+        <v>27</v>
+      </c>
+      <c r="L76" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77">
+        <v>2018</v>
+      </c>
+      <c r="D77" t="s">
+        <v>32</v>
+      </c>
+      <c r="E77">
+        <v>678</v>
+      </c>
+      <c r="F77">
+        <v>430</v>
+      </c>
+      <c r="G77">
+        <v>11.5</v>
+      </c>
+      <c r="H77">
+        <v>1230458</v>
+      </c>
+      <c r="I77">
+        <v>120</v>
+      </c>
+      <c r="J77">
+        <v>63</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
+      <c r="L77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78">
+        <v>2023</v>
+      </c>
+      <c r="D78" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78">
+        <v>989</v>
+      </c>
+      <c r="F78">
+        <v>91</v>
+      </c>
+      <c r="G78">
+        <v>18.2</v>
+      </c>
+      <c r="H78">
+        <v>2014177</v>
+      </c>
+      <c r="I78">
+        <v>166</v>
+      </c>
+      <c r="J78">
+        <v>92</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79">
+        <v>2024</v>
+      </c>
+      <c r="D79" t="s">
+        <v>32</v>
+      </c>
+      <c r="E79">
+        <v>881</v>
+      </c>
+      <c r="F79">
+        <v>325</v>
+      </c>
+      <c r="G79">
+        <v>11</v>
+      </c>
+      <c r="H79">
+        <v>1102844</v>
+      </c>
+      <c r="I79">
+        <v>92</v>
+      </c>
+      <c r="J79">
+        <v>83</v>
+      </c>
+      <c r="K79" t="s">
+        <v>15</v>
+      </c>
+      <c r="L79" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80">
+        <v>2021</v>
+      </c>
+      <c r="D80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80">
+        <v>113</v>
+      </c>
+      <c r="F80">
+        <v>113</v>
+      </c>
+      <c r="G80">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="H80">
+        <v>1943470</v>
+      </c>
+      <c r="I80">
+        <v>169</v>
+      </c>
+      <c r="J80">
+        <v>93</v>
+      </c>
+      <c r="K80" t="s">
+        <v>27</v>
+      </c>
+      <c r="L80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>25</v>
+      </c>
+      <c r="B81" t="s">
+        <v>35</v>
+      </c>
+      <c r="C81">
+        <v>2019</v>
+      </c>
+      <c r="D81" t="s">
+        <v>32</v>
+      </c>
+      <c r="E81">
+        <v>443</v>
+      </c>
+      <c r="F81">
+        <v>443</v>
+      </c>
+      <c r="G81">
+        <v>5.9</v>
+      </c>
+      <c r="H81">
+        <v>1528422</v>
+      </c>
+      <c r="I81">
+        <v>127</v>
+      </c>
+      <c r="J81">
+        <v>62</v>
+      </c>
+      <c r="K81" t="s">
+        <v>27</v>
+      </c>
+      <c r="L81" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" t="s">
+        <v>36</v>
+      </c>
+      <c r="C82">
+        <v>2019</v>
+      </c>
+      <c r="D82" t="s">
+        <v>34</v>
+      </c>
+      <c r="E82">
+        <v>391</v>
+      </c>
+      <c r="F82">
+        <v>328</v>
+      </c>
+      <c r="G82">
+        <v>7.3</v>
+      </c>
+      <c r="H82">
+        <v>756601</v>
+      </c>
+      <c r="I82">
+        <v>65</v>
+      </c>
+      <c r="J82">
+        <v>92</v>
+      </c>
+      <c r="K82" t="s">
+        <v>27</v>
+      </c>
+      <c r="L82" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83">
+        <v>2019</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83">
+        <v>455</v>
+      </c>
+      <c r="F83">
+        <v>455</v>
+      </c>
+      <c r="G83">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="H83">
+        <v>1976097</v>
+      </c>
+      <c r="I83">
+        <v>127</v>
+      </c>
+      <c r="J83">
+        <v>97</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84">
+        <v>2024</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84">
+        <v>997</v>
+      </c>
+      <c r="F84">
+        <v>358</v>
+      </c>
+      <c r="G84">
+        <v>6.1</v>
+      </c>
+      <c r="H84">
+        <v>2376485</v>
+      </c>
+      <c r="I84">
+        <v>192</v>
+      </c>
+      <c r="J84">
+        <v>74</v>
+      </c>
+      <c r="K84" t="s">
+        <v>27</v>
+      </c>
+      <c r="L84" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85">
+        <v>2019</v>
+      </c>
+      <c r="D85" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85">
+        <v>189</v>
+      </c>
+      <c r="F85">
+        <v>189</v>
+      </c>
+      <c r="G85">
+        <v>5</v>
+      </c>
+      <c r="H85">
+        <v>816666</v>
+      </c>
+      <c r="I85">
+        <v>112</v>
+      </c>
+      <c r="J85">
+        <v>86</v>
+      </c>
+      <c r="K85" t="s">
+        <v>27</v>
+      </c>
+      <c r="L85" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>21</v>
+      </c>
+      <c r="C86">
+        <v>2020</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86">
+        <v>883</v>
+      </c>
+      <c r="F86">
+        <v>158</v>
+      </c>
+      <c r="G86">
+        <v>7.5</v>
+      </c>
+      <c r="H86">
+        <v>1683422</v>
+      </c>
+      <c r="I86">
+        <v>127</v>
+      </c>
+      <c r="J86">
+        <v>83</v>
+      </c>
+      <c r="K86" t="s">
+        <v>27</v>
+      </c>
+      <c r="L86" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>35</v>
+      </c>
+      <c r="C87">
+        <v>2022</v>
+      </c>
+      <c r="D87" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87">
+        <v>202</v>
+      </c>
+      <c r="F87">
+        <v>202</v>
+      </c>
+      <c r="G87">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H87">
+        <v>817129</v>
+      </c>
+      <c r="I87">
+        <v>45</v>
+      </c>
+      <c r="J87">
+        <v>78</v>
+      </c>
+      <c r="K87" t="s">
+        <v>19</v>
+      </c>
+      <c r="L87" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88">
+        <v>2019</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88">
+        <v>401</v>
+      </c>
+      <c r="F88">
+        <v>401</v>
+      </c>
+      <c r="G88">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H88">
+        <v>1247068</v>
+      </c>
+      <c r="I88">
+        <v>95</v>
+      </c>
+      <c r="J88">
+        <v>75</v>
+      </c>
+      <c r="K88" t="s">
+        <v>19</v>
+      </c>
+      <c r="L88" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89">
+        <v>2019</v>
+      </c>
+      <c r="D89" t="s">
+        <v>22</v>
+      </c>
+      <c r="E89">
+        <v>600</v>
+      </c>
+      <c r="F89">
+        <v>227</v>
+      </c>
+      <c r="G89">
+        <v>3.1</v>
+      </c>
+      <c r="H89">
+        <v>2362675</v>
+      </c>
+      <c r="I89">
+        <v>169</v>
+      </c>
+      <c r="J89">
+        <v>65</v>
+      </c>
+      <c r="K89" t="s">
+        <v>19</v>
+      </c>
+      <c r="L89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+      <c r="C90">
+        <v>2019</v>
+      </c>
+      <c r="D90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90">
+        <v>123</v>
+      </c>
+      <c r="F90">
+        <v>123</v>
+      </c>
+      <c r="G90">
+        <v>18</v>
+      </c>
+      <c r="H90">
+        <v>1089878</v>
+      </c>
+      <c r="I90">
+        <v>170</v>
+      </c>
+      <c r="J90">
+        <v>70</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" t="s">
+        <v>28</v>
+      </c>
+      <c r="C91">
+        <v>2021</v>
+      </c>
+      <c r="D91" t="s">
+        <v>34</v>
+      </c>
+      <c r="E91">
+        <v>526</v>
+      </c>
+      <c r="F91">
+        <v>495</v>
+      </c>
+      <c r="G91">
+        <v>16</v>
+      </c>
+      <c r="H91">
+        <v>1256584</v>
+      </c>
+      <c r="I91">
+        <v>140</v>
+      </c>
+      <c r="J91">
+        <v>78</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>25</v>
+      </c>
+      <c r="B92" t="s">
+        <v>35</v>
+      </c>
+      <c r="C92">
+        <v>2024</v>
+      </c>
+      <c r="D92" t="s">
+        <v>22</v>
+      </c>
+      <c r="E92">
+        <v>225</v>
+      </c>
+      <c r="F92">
+        <v>225</v>
+      </c>
+      <c r="G92">
+        <v>7.7</v>
+      </c>
+      <c r="H92">
+        <v>582124</v>
+      </c>
+      <c r="I92">
+        <v>186</v>
+      </c>
+      <c r="J92">
+        <v>91</v>
+      </c>
+      <c r="K92" t="s">
+        <v>27</v>
+      </c>
+      <c r="L92" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>25</v>
+      </c>
+      <c r="B93" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93">
+        <v>2024</v>
+      </c>
+      <c r="D93" t="s">
+        <v>34</v>
+      </c>
+      <c r="E93">
+        <v>429</v>
+      </c>
+      <c r="F93">
+        <v>422</v>
+      </c>
+      <c r="G93">
+        <v>9.5</v>
+      </c>
+      <c r="H93">
+        <v>537208</v>
+      </c>
+      <c r="I93">
+        <v>92</v>
+      </c>
+      <c r="J93">
+        <v>83</v>
+      </c>
+      <c r="K93" t="s">
+        <v>27</v>
+      </c>
+      <c r="L93" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>25</v>
+      </c>
+      <c r="B94" t="s">
+        <v>38</v>
+      </c>
+      <c r="C94">
+        <v>2021</v>
+      </c>
+      <c r="D94" t="s">
+        <v>34</v>
+      </c>
+      <c r="E94">
+        <v>131</v>
+      </c>
+      <c r="F94">
+        <v>131</v>
+      </c>
+      <c r="G94">
+        <v>5.6</v>
+      </c>
+      <c r="H94">
+        <v>1617598</v>
+      </c>
+      <c r="I94">
+        <v>137</v>
+      </c>
+      <c r="J94">
+        <v>92</v>
+      </c>
+      <c r="K94" t="s">
+        <v>27</v>
+      </c>
+      <c r="L94" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" t="s">
+        <v>21</v>
+      </c>
+      <c r="C95">
+        <v>2018</v>
+      </c>
+      <c r="D95" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95">
+        <v>503</v>
+      </c>
+      <c r="F95">
+        <v>503</v>
+      </c>
+      <c r="G95">
+        <v>4.5</v>
+      </c>
+      <c r="H95">
+        <v>1684704</v>
+      </c>
+      <c r="I95">
+        <v>54</v>
+      </c>
+      <c r="J95">
+        <v>83</v>
+      </c>
+      <c r="K95" t="s">
+        <v>19</v>
+      </c>
+      <c r="L95" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" t="s">
+        <v>36</v>
+      </c>
+      <c r="C96">
+        <v>2018</v>
+      </c>
+      <c r="D96" t="s">
+        <v>22</v>
+      </c>
+      <c r="E96">
+        <v>191</v>
+      </c>
+      <c r="F96">
+        <v>191</v>
+      </c>
+      <c r="G96">
+        <v>13.9</v>
+      </c>
+      <c r="H96">
+        <v>2056764</v>
+      </c>
+      <c r="I96">
+        <v>153</v>
+      </c>
+      <c r="J96">
+        <v>75</v>
+      </c>
+      <c r="K96" t="s">
+        <v>15</v>
+      </c>
+      <c r="L96" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97">
+        <v>2023</v>
+      </c>
+      <c r="D97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97">
+        <v>229</v>
+      </c>
+      <c r="F97">
+        <v>229</v>
+      </c>
+      <c r="G97">
+        <v>5.9</v>
+      </c>
+      <c r="H97">
+        <v>837328</v>
+      </c>
+      <c r="I97">
+        <v>94</v>
+      </c>
+      <c r="J97">
+        <v>62</v>
+      </c>
+      <c r="K97" t="s">
+        <v>27</v>
+      </c>
+      <c r="L97" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" t="s">
+        <v>40</v>
+      </c>
+      <c r="C98">
+        <v>2019</v>
+      </c>
+      <c r="D98" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98">
+        <v>324</v>
+      </c>
+      <c r="F98">
+        <v>324</v>
+      </c>
+      <c r="G98">
+        <v>8.9</v>
+      </c>
+      <c r="H98">
+        <v>511770</v>
+      </c>
+      <c r="I98">
+        <v>125</v>
+      </c>
+      <c r="J98">
+        <v>75</v>
+      </c>
+      <c r="K98" t="s">
+        <v>27</v>
+      </c>
+      <c r="L98" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>13</v>
+      </c>
+      <c r="C99">
+        <v>2018</v>
+      </c>
+      <c r="D99" t="s">
+        <v>34</v>
+      </c>
+      <c r="E99">
+        <v>565</v>
+      </c>
+      <c r="F99">
+        <v>565</v>
+      </c>
+      <c r="G99">
+        <v>16.8</v>
+      </c>
+      <c r="H99">
+        <v>1960762</v>
+      </c>
+      <c r="I99">
+        <v>47</v>
+      </c>
+      <c r="J99">
+        <v>79</v>
+      </c>
+      <c r="K99" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B100" t="s">
+        <v>28</v>
+      </c>
+      <c r="C100">
+        <v>2018</v>
+      </c>
+      <c r="D100" t="s">
+        <v>14</v>
+      </c>
+      <c r="E100">
+        <v>828</v>
+      </c>
+      <c r="F100">
+        <v>212</v>
+      </c>
+      <c r="G100">
+        <v>13</v>
+      </c>
+      <c r="H100">
+        <v>2410635</v>
+      </c>
+      <c r="I100">
+        <v>124</v>
+      </c>
+      <c r="J100">
+        <v>62</v>
+      </c>
+      <c r="K100" t="s">
+        <v>15</v>
+      </c>
+      <c r="L100" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" t="s">
+        <v>38</v>
+      </c>
+      <c r="C101">
+        <v>2024</v>
+      </c>
+      <c r="D101" t="s">
+        <v>32</v>
+      </c>
+      <c r="E101">
+        <v>671</v>
+      </c>
+      <c r="F101">
+        <v>356</v>
+      </c>
+      <c r="G101">
+        <v>10.7</v>
+      </c>
+      <c r="H101">
+        <v>846937</v>
+      </c>
+      <c r="I101">
+        <v>125</v>
+      </c>
+      <c r="J101">
+        <v>94</v>
+      </c>
+      <c r="K101" t="s">
+        <v>15</v>
+      </c>
+      <c r="L101" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102" t="s">
+        <v>21</v>
+      </c>
+      <c r="C102">
+        <v>2022</v>
+      </c>
+      <c r="D102" t="s">
+        <v>12</v>
+      </c>
+      <c r="E102">
+        <v>710</v>
+      </c>
+      <c r="F102">
+        <v>710</v>
+      </c>
+      <c r="G102">
+        <v>8</v>
+      </c>
+      <c r="H102">
+        <v>1942228</v>
+      </c>
+      <c r="I102">
+        <v>123</v>
+      </c>
+      <c r="J102">
+        <v>82</v>
+      </c>
+      <c r="K102" t="s">
+        <v>27</v>
+      </c>
+      <c r="L102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>25</v>
+      </c>
+      <c r="B103" t="s">
+        <v>36</v>
+      </c>
+      <c r="C103">
+        <v>2018</v>
+      </c>
+      <c r="D103" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103">
+        <v>257</v>
+      </c>
+      <c r="F103">
+        <v>257</v>
+      </c>
+      <c r="G103">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H103">
+        <v>996782</v>
+      </c>
+      <c r="I103">
+        <v>59</v>
+      </c>
+      <c r="J103">
+        <v>77</v>
+      </c>
+      <c r="K103" t="s">
+        <v>19</v>
+      </c>
+      <c r="L103" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104">
+        <v>2024</v>
+      </c>
+      <c r="D104" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104">
+        <v>465</v>
+      </c>
+      <c r="F104">
+        <v>465</v>
+      </c>
+      <c r="G104">
+        <v>15.1</v>
+      </c>
+      <c r="H104">
+        <v>1423196</v>
+      </c>
+      <c r="I104">
+        <v>58</v>
+      </c>
+      <c r="J104">
+        <v>68</v>
+      </c>
+      <c r="K104" t="s">
+        <v>23</v>
+      </c>
+      <c r="L104" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>12</v>
+      </c>
+      <c r="B105" t="s">
+        <v>13</v>
+      </c>
+      <c r="C105">
+        <v>2022</v>
+      </c>
+      <c r="D105" t="s">
+        <v>32</v>
+      </c>
+      <c r="E105">
+        <v>322</v>
+      </c>
+      <c r="F105">
+        <v>322</v>
+      </c>
+      <c r="G105">
+        <v>12.6</v>
+      </c>
+      <c r="H105">
+        <v>1879492</v>
+      </c>
+      <c r="I105">
+        <v>191</v>
+      </c>
+      <c r="J105">
+        <v>89</v>
+      </c>
+      <c r="K105" t="s">
+        <v>15</v>
+      </c>
+      <c r="L105" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106">
+        <v>2022</v>
+      </c>
+      <c r="D106" t="s">
+        <v>14</v>
+      </c>
+      <c r="E106">
+        <v>422</v>
+      </c>
+      <c r="F106">
+        <v>422</v>
+      </c>
+      <c r="G106">
+        <v>17.2</v>
+      </c>
+      <c r="H106">
+        <v>995843</v>
+      </c>
+      <c r="I106">
+        <v>102</v>
+      </c>
+      <c r="J106">
+        <v>97</v>
+      </c>
+      <c r="K106" t="s">
+        <v>23</v>
+      </c>
+      <c r="L106" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>25</v>
+      </c>
+      <c r="B107" t="s">
+        <v>38</v>
+      </c>
+      <c r="C107">
+        <v>2022</v>
+      </c>
+      <c r="D107" t="s">
+        <v>18</v>
+      </c>
+      <c r="E107">
+        <v>642</v>
+      </c>
+      <c r="F107">
+        <v>103</v>
+      </c>
+      <c r="G107">
+        <v>9.1</v>
+      </c>
+      <c r="H107">
+        <v>521631</v>
+      </c>
+      <c r="I107">
+        <v>112</v>
+      </c>
+      <c r="J107">
+        <v>98</v>
+      </c>
+      <c r="K107" t="s">
+        <v>27</v>
+      </c>
+      <c r="L107" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>12</v>
+      </c>
+      <c r="B108" t="s">
+        <v>36</v>
+      </c>
+      <c r="C108">
+        <v>2022</v>
+      </c>
+      <c r="D108" t="s">
+        <v>29</v>
+      </c>
+      <c r="E108">
+        <v>385</v>
+      </c>
+      <c r="F108">
+        <v>348</v>
+      </c>
+      <c r="G108">
+        <v>19.8</v>
+      </c>
+      <c r="H108">
+        <v>1712575</v>
+      </c>
+      <c r="I108">
+        <v>111</v>
+      </c>
+      <c r="J108">
+        <v>89</v>
+      </c>
+      <c r="K108" t="s">
+        <v>23</v>
+      </c>
+      <c r="L108" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>25</v>
+      </c>
+      <c r="B109" t="s">
+        <v>36</v>
+      </c>
+      <c r="C109">
+        <v>2020</v>
+      </c>
+      <c r="D109" t="s">
+        <v>22</v>
+      </c>
+      <c r="E109">
+        <v>162</v>
+      </c>
+      <c r="F109">
+        <v>85</v>
+      </c>
+      <c r="G109">
+        <v>10.6</v>
+      </c>
+      <c r="H109">
+        <v>727020</v>
+      </c>
+      <c r="I109">
+        <v>121</v>
+      </c>
+      <c r="J109">
+        <v>92</v>
+      </c>
+      <c r="K109" t="s">
+        <v>15</v>
+      </c>
+      <c r="L109" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s">
+        <v>31</v>
+      </c>
+      <c r="C110">
+        <v>2024</v>
+      </c>
+      <c r="D110" t="s">
+        <v>12</v>
+      </c>
+      <c r="E110">
+        <v>946</v>
+      </c>
+      <c r="F110">
+        <v>104</v>
+      </c>
+      <c r="G110">
+        <v>18.2</v>
+      </c>
+      <c r="H110">
+        <v>2287216</v>
+      </c>
+      <c r="I110">
+        <v>99</v>
+      </c>
+      <c r="J110">
+        <v>61</v>
+      </c>
+      <c r="K110" t="s">
+        <v>23</v>
+      </c>
+      <c r="L110" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>12</v>
+      </c>
+      <c r="B111" t="s">
+        <v>33</v>
+      </c>
+      <c r="C111">
+        <v>2021</v>
+      </c>
+      <c r="D111" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111">
+        <v>825</v>
+      </c>
+      <c r="F111">
+        <v>597</v>
+      </c>
+      <c r="G111">
+        <v>10.7</v>
+      </c>
+      <c r="H111">
+        <v>617319</v>
+      </c>
+      <c r="I111">
+        <v>185</v>
+      </c>
+      <c r="J111">
+        <v>78</v>
+      </c>
+      <c r="K111" t="s">
+        <v>15</v>
+      </c>
+      <c r="L111" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>25</v>
+      </c>
+      <c r="B112" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112">
+        <v>2021</v>
+      </c>
+      <c r="D112" t="s">
+        <v>14</v>
+      </c>
+      <c r="E112">
+        <v>966</v>
+      </c>
+      <c r="F112">
+        <v>856</v>
+      </c>
+      <c r="G112">
+        <v>15.3</v>
+      </c>
+      <c r="H112">
+        <v>769162</v>
+      </c>
+      <c r="I112">
+        <v>39</v>
+      </c>
+      <c r="J112">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s">
+        <v>23</v>
+      </c>
+      <c r="L112" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>12</v>
+      </c>
+      <c r="B113" t="s">
+        <v>38</v>
+      </c>
+      <c r="C113">
+        <v>2022</v>
+      </c>
+      <c r="D113" t="s">
+        <v>29</v>
+      </c>
+      <c r="E113">
+        <v>365</v>
+      </c>
+      <c r="F113">
+        <v>365</v>
+      </c>
+      <c r="G113">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="H113">
+        <v>760860</v>
+      </c>
+      <c r="I113">
+        <v>128</v>
+      </c>
+      <c r="J113">
+        <v>72</v>
+      </c>
+      <c r="K113" t="s">
+        <v>23</v>
+      </c>
+      <c r="L113" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>25</v>
+      </c>
+      <c r="B114" t="s">
+        <v>13</v>
+      </c>
+      <c r="C114">
+        <v>2023</v>
+      </c>
+      <c r="D114" t="s">
+        <v>29</v>
+      </c>
+      <c r="E114">
+        <v>187</v>
+      </c>
+      <c r="F114">
+        <v>187</v>
+      </c>
+      <c r="G114">
+        <v>3.3</v>
+      </c>
+      <c r="H114">
+        <v>1601663</v>
+      </c>
+      <c r="I114">
+        <v>74</v>
+      </c>
+      <c r="J114">
+        <v>79</v>
+      </c>
+      <c r="K114" t="s">
+        <v>19</v>
+      </c>
+      <c r="L114" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>12</v>
+      </c>
+      <c r="B115" t="s">
+        <v>31</v>
+      </c>
+      <c r="C115">
+        <v>2022</v>
+      </c>
+      <c r="D115" t="s">
+        <v>34</v>
+      </c>
+      <c r="E115">
+        <v>571</v>
+      </c>
+      <c r="F115">
+        <v>516</v>
+      </c>
+      <c r="G115">
+        <v>11.4</v>
+      </c>
+      <c r="H115">
+        <v>1213092</v>
+      </c>
+      <c r="I115">
+        <v>82</v>
+      </c>
+      <c r="J115">
+        <v>90</v>
+      </c>
+      <c r="K115" t="s">
+        <v>15</v>
+      </c>
+      <c r="L115" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>12</v>
+      </c>
+      <c r="B116" t="s">
+        <v>36</v>
+      </c>
+      <c r="C116">
+        <v>2021</v>
+      </c>
+      <c r="D116" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116">
+        <v>907</v>
+      </c>
+      <c r="F116">
+        <v>575</v>
+      </c>
+      <c r="G116">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="H116">
+        <v>1374498</v>
+      </c>
+      <c r="I116">
+        <v>161</v>
+      </c>
+      <c r="J116">
+        <v>68</v>
+      </c>
+      <c r="K116" t="s">
+        <v>23</v>
+      </c>
+      <c r="L116" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>12</v>
+      </c>
+      <c r="B117" t="s">
+        <v>39</v>
+      </c>
+      <c r="C117">
+        <v>2020</v>
+      </c>
+      <c r="D117" t="s">
+        <v>29</v>
+      </c>
+      <c r="E117">
+        <v>912</v>
+      </c>
+      <c r="F117">
+        <v>692</v>
+      </c>
+      <c r="G117">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="H117">
+        <v>974017</v>
+      </c>
+      <c r="I117">
+        <v>197</v>
+      </c>
+      <c r="J117">
+        <v>62</v>
+      </c>
+      <c r="K117" t="s">
+        <v>23</v>
+      </c>
+      <c r="L117" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>12</v>
+      </c>
+      <c r="B118" t="s">
+        <v>13</v>
+      </c>
+      <c r="C118">
+        <v>2020</v>
+      </c>
+      <c r="D118" t="s">
+        <v>32</v>
+      </c>
+      <c r="E118">
+        <v>910</v>
+      </c>
+      <c r="F118">
+        <v>443</v>
+      </c>
+      <c r="G118">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="H118">
+        <v>1283053</v>
+      </c>
+      <c r="I118">
+        <v>103</v>
+      </c>
+      <c r="J118">
+        <v>78</v>
+      </c>
+      <c r="K118" t="s">
+        <v>23</v>
+      </c>
+      <c r="L118" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>12</v>
+      </c>
+      <c r="B119" t="s">
+        <v>28</v>
+      </c>
+      <c r="C119">
+        <v>2024</v>
+      </c>
+      <c r="D119" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119">
+        <v>815</v>
+      </c>
+      <c r="F119">
+        <v>815</v>
+      </c>
+      <c r="G119">
+        <v>9.9</v>
+      </c>
+      <c r="H119">
+        <v>2273813</v>
+      </c>
+      <c r="I119">
+        <v>94</v>
+      </c>
+      <c r="J119">
+        <v>86</v>
+      </c>
+      <c r="K119" t="s">
+        <v>27</v>
+      </c>
+      <c r="L119" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>12</v>
+      </c>
+      <c r="B120" t="s">
+        <v>35</v>
+      </c>
+      <c r="C120">
+        <v>2024</v>
+      </c>
+      <c r="D120" t="s">
+        <v>18</v>
+      </c>
+      <c r="E120">
+        <v>475</v>
+      </c>
+      <c r="F120">
+        <v>57</v>
+      </c>
+      <c r="G120">
+        <v>12.2</v>
+      </c>
+      <c r="H120">
+        <v>1433798</v>
+      </c>
+      <c r="I120">
+        <v>83</v>
+      </c>
+      <c r="J120">
+        <v>95</v>
+      </c>
+      <c r="K120" t="s">
+        <v>15</v>
+      </c>
+      <c r="L120" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>12</v>
+      </c>
+      <c r="B121" t="s">
+        <v>38</v>
+      </c>
+      <c r="C121">
+        <v>2019</v>
+      </c>
+      <c r="D121" t="s">
+        <v>22</v>
+      </c>
+      <c r="E121">
+        <v>832</v>
+      </c>
+      <c r="F121">
+        <v>87</v>
+      </c>
+      <c r="G121">
+        <v>5.5</v>
+      </c>
+      <c r="H121">
+        <v>2483796</v>
+      </c>
+      <c r="I121">
+        <v>194</v>
+      </c>
+      <c r="J121">
+        <v>80</v>
+      </c>
+      <c r="K121" t="s">
+        <v>27</v>
+      </c>
+      <c r="L121" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>12</v>
+      </c>
+      <c r="B122" t="s">
+        <v>39</v>
+      </c>
+      <c r="C122">
+        <v>2020</v>
+      </c>
+      <c r="D122" t="s">
+        <v>34</v>
+      </c>
+      <c r="E122">
+        <v>610</v>
+      </c>
+      <c r="F122">
+        <v>170</v>
+      </c>
+      <c r="G122">
+        <v>12.4</v>
+      </c>
+      <c r="H122">
+        <v>1131552</v>
+      </c>
+      <c r="I122">
+        <v>185</v>
+      </c>
+      <c r="J122">
+        <v>89</v>
+      </c>
+      <c r="K122" t="s">
+        <v>15</v>
+      </c>
+      <c r="L122" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>12</v>
+      </c>
+      <c r="B123" t="s">
+        <v>38</v>
+      </c>
+      <c r="C123">
+        <v>2020</v>
+      </c>
+      <c r="D123" t="s">
+        <v>29</v>
+      </c>
+      <c r="E123">
+        <v>287</v>
+      </c>
+      <c r="F123">
+        <v>287</v>
+      </c>
+      <c r="G123">
+        <v>16.8</v>
+      </c>
+      <c r="H123">
+        <v>615003</v>
+      </c>
+      <c r="I123">
+        <v>81</v>
+      </c>
+      <c r="J123">
+        <v>81</v>
+      </c>
+      <c r="K123" t="s">
+        <v>23</v>
+      </c>
+      <c r="L123" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>12</v>
+      </c>
+      <c r="B124" t="s">
+        <v>38</v>
+      </c>
+      <c r="C124">
+        <v>2022</v>
+      </c>
+      <c r="D124" t="s">
+        <v>22</v>
+      </c>
+      <c r="E124">
+        <v>823</v>
+      </c>
+      <c r="F124">
+        <v>281</v>
+      </c>
+      <c r="G124">
+        <v>13</v>
+      </c>
+      <c r="H124">
+        <v>1358069</v>
+      </c>
+      <c r="I124">
+        <v>152</v>
+      </c>
+      <c r="J124">
+        <v>71</v>
+      </c>
+      <c r="K124" t="s">
+        <v>15</v>
+      </c>
+      <c r="L124" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>12</v>
+      </c>
+      <c r="B125" t="s">
+        <v>26</v>
+      </c>
+      <c r="C125">
+        <v>2024</v>
+      </c>
+      <c r="D125" t="s">
+        <v>22</v>
+      </c>
+      <c r="E125">
+        <v>549</v>
+      </c>
+      <c r="F125">
+        <v>549</v>
+      </c>
+      <c r="G125">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="H125">
+        <v>998360</v>
+      </c>
+      <c r="I125">
+        <v>154</v>
+      </c>
+      <c r="J125">
+        <v>87</v>
+      </c>
+      <c r="K125" t="s">
+        <v>27</v>
+      </c>
+      <c r="L125" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>12</v>
+      </c>
+      <c r="B126" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126">
+        <v>2023</v>
+      </c>
+      <c r="D126" t="s">
+        <v>14</v>
+      </c>
+      <c r="E126">
+        <v>858</v>
+      </c>
+      <c r="F126">
+        <v>505</v>
+      </c>
+      <c r="G126">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H126">
+        <v>1031610</v>
+      </c>
+      <c r="I126">
+        <v>81</v>
+      </c>
+      <c r="J126">
+        <v>86</v>
+      </c>
+      <c r="K126" t="s">
+        <v>27</v>
+      </c>
+      <c r="L126" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>12</v>
+      </c>
+      <c r="B127" t="s">
+        <v>13</v>
+      </c>
+      <c r="C127">
+        <v>2021</v>
+      </c>
+      <c r="D127" t="s">
+        <v>14</v>
+      </c>
+      <c r="E127">
+        <v>316</v>
+      </c>
+      <c r="F127">
+        <v>250</v>
+      </c>
+      <c r="G127">
+        <v>7.6</v>
+      </c>
+      <c r="H127">
+        <v>1142272</v>
+      </c>
+      <c r="I127">
+        <v>163</v>
+      </c>
+      <c r="J127">
+        <v>88</v>
+      </c>
+      <c r="K127" t="s">
+        <v>27</v>
+      </c>
+      <c r="L127" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>25</v>
+      </c>
+      <c r="B128" t="s">
+        <v>21</v>
+      </c>
+      <c r="C128">
+        <v>2022</v>
+      </c>
+      <c r="D128" t="s">
+        <v>34</v>
+      </c>
+      <c r="E128">
+        <v>326</v>
+      </c>
+      <c r="F128">
+        <v>326</v>
+      </c>
+      <c r="G128">
+        <v>4.7</v>
+      </c>
+      <c r="H128">
+        <v>1583423</v>
+      </c>
+      <c r="I128">
+        <v>59</v>
+      </c>
+      <c r="J128">
+        <v>94</v>
+      </c>
+      <c r="K128" t="s">
+        <v>19</v>
+      </c>
+      <c r="L128" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>25</v>
+      </c>
+      <c r="B129" t="s">
+        <v>35</v>
+      </c>
+      <c r="C129">
+        <v>2018</v>
+      </c>
+      <c r="D129" t="s">
+        <v>29</v>
+      </c>
+      <c r="E129">
+        <v>696</v>
+      </c>
+      <c r="F129">
+        <v>673</v>
+      </c>
+      <c r="G129">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H129">
+        <v>1199659</v>
+      </c>
+      <c r="I129">
+        <v>151</v>
+      </c>
+      <c r="J129">
+        <v>97</v>
+      </c>
+      <c r="K129" t="s">
+        <v>27</v>
+      </c>
+      <c r="L129" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>12</v>
+      </c>
+      <c r="B130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130">
+        <v>2024</v>
+      </c>
+      <c r="D130" t="s">
+        <v>14</v>
+      </c>
+      <c r="E130">
+        <v>387</v>
+      </c>
+      <c r="F130">
+        <v>282</v>
+      </c>
+      <c r="G130">
+        <v>7.2</v>
+      </c>
+      <c r="H130">
+        <v>528793</v>
+      </c>
+      <c r="I130">
+        <v>158</v>
+      </c>
+      <c r="J130">
+        <v>78</v>
+      </c>
+      <c r="K130" t="s">
+        <v>27</v>
+      </c>
+      <c r="L130" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>12</v>
+      </c>
+      <c r="B131" t="s">
+        <v>38</v>
+      </c>
+      <c r="C131">
+        <v>2020</v>
+      </c>
+      <c r="D131" t="s">
+        <v>32</v>
+      </c>
+      <c r="E131">
+        <v>191</v>
+      </c>
+      <c r="F131">
+        <v>191</v>
+      </c>
+      <c r="G131">
+        <v>3</v>
+      </c>
+      <c r="H131">
+        <v>1377250</v>
+      </c>
+      <c r="I131">
+        <v>161</v>
+      </c>
+      <c r="J131">
+        <v>64</v>
+      </c>
+      <c r="K131" t="s">
+        <v>19</v>
+      </c>
+      <c r="L131" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>25</v>
+      </c>
+      <c r="B132" t="s">
+        <v>38</v>
+      </c>
+      <c r="C132">
+        <v>2023</v>
+      </c>
+      <c r="D132" t="s">
+        <v>34</v>
+      </c>
+      <c r="E132">
+        <v>903</v>
+      </c>
+      <c r="F132">
+        <v>579</v>
+      </c>
+      <c r="G132">
+        <v>18.5</v>
+      </c>
+      <c r="H132">
+        <v>1153765</v>
+      </c>
+      <c r="I132">
+        <v>189</v>
+      </c>
+      <c r="J132">
+        <v>65</v>
+      </c>
+      <c r="K132" t="s">
+        <v>23</v>
+      </c>
+      <c r="L132" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>12</v>
+      </c>
+      <c r="B133" t="s">
+        <v>21</v>
+      </c>
+      <c r="C133">
+        <v>2023</v>
+      </c>
+      <c r="D133" t="s">
+        <v>14</v>
+      </c>
+      <c r="E133">
+        <v>209</v>
+      </c>
+      <c r="F133">
+        <v>209</v>
+      </c>
+      <c r="G133">
+        <v>6.3</v>
+      </c>
+      <c r="H133">
+        <v>1600559</v>
+      </c>
+      <c r="I133">
+        <v>189</v>
+      </c>
+      <c r="J133">
+        <v>76</v>
+      </c>
+      <c r="K133" t="s">
+        <v>27</v>
+      </c>
+      <c r="L133" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>12</v>
+      </c>
+      <c r="B134" t="s">
+        <v>38</v>
+      </c>
+      <c r="C134">
+        <v>2021</v>
+      </c>
+      <c r="D134" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134">
+        <v>810</v>
+      </c>
+      <c r="F134">
+        <v>399</v>
+      </c>
+      <c r="G134">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="H134">
+        <v>649358</v>
+      </c>
+      <c r="I134">
+        <v>79</v>
+      </c>
+      <c r="J134">
+        <v>68</v>
+      </c>
+      <c r="K134" t="s">
+        <v>23</v>
+      </c>
+      <c r="L134" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>25</v>
+      </c>
+      <c r="B135" t="s">
+        <v>21</v>
+      </c>
+      <c r="C135">
+        <v>2019</v>
+      </c>
+      <c r="D135" t="s">
+        <v>14</v>
+      </c>
+      <c r="E135">
+        <v>171</v>
+      </c>
+      <c r="F135">
+        <v>171</v>
+      </c>
+      <c r="G135">
+        <v>4.2</v>
+      </c>
+      <c r="H135">
+        <v>2458521</v>
+      </c>
+      <c r="I135">
+        <v>196</v>
+      </c>
+      <c r="J135">
+        <v>74</v>
+      </c>
+      <c r="K135" t="s">
+        <v>19</v>
+      </c>
+      <c r="L135" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>12</v>
+      </c>
+      <c r="B136" t="s">
+        <v>26</v>
+      </c>
+      <c r="C136">
+        <v>2024</v>
+      </c>
+      <c r="D136" t="s">
+        <v>22</v>
+      </c>
+      <c r="E136">
+        <v>882</v>
+      </c>
+      <c r="F136">
+        <v>754</v>
+      </c>
+      <c r="G136">
+        <v>18.3</v>
+      </c>
+      <c r="H136">
+        <v>1832145</v>
+      </c>
+      <c r="I136">
+        <v>146</v>
+      </c>
+      <c r="J136">
+        <v>98</v>
+      </c>
+      <c r="K136" t="s">
+        <v>23</v>
+      </c>
+      <c r="L136" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137" t="s">
+        <v>17</v>
+      </c>
+      <c r="C137">
+        <v>2018</v>
+      </c>
+      <c r="D137" t="s">
+        <v>32</v>
+      </c>
+      <c r="E137">
+        <v>554</v>
+      </c>
+      <c r="F137">
+        <v>502</v>
+      </c>
+      <c r="G137">
+        <v>19.8</v>
+      </c>
+      <c r="H137">
+        <v>1825420</v>
+      </c>
+      <c r="I137">
+        <v>161</v>
+      </c>
+      <c r="J137">
+        <v>70</v>
+      </c>
+      <c r="K137" t="s">
+        <v>23</v>
+      </c>
+      <c r="L137" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>12</v>
+      </c>
+      <c r="B138" t="s">
+        <v>13</v>
+      </c>
+      <c r="C138">
+        <v>2022</v>
+      </c>
+      <c r="D138" t="s">
+        <v>22</v>
+      </c>
+      <c r="E138">
+        <v>131</v>
+      </c>
+      <c r="F138">
+        <v>131</v>
+      </c>
+      <c r="G138">
+        <v>13.6</v>
+      </c>
+      <c r="H138">
+        <v>530476</v>
+      </c>
+      <c r="I138">
+        <v>133</v>
+      </c>
+      <c r="J138">
+        <v>68</v>
+      </c>
+      <c r="K138" t="s">
+        <v>15</v>
+      </c>
+      <c r="L138" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>25</v>
+      </c>
+      <c r="B139" t="s">
+        <v>28</v>
+      </c>
+      <c r="C139">
+        <v>2019</v>
+      </c>
+      <c r="D139" t="s">
+        <v>14</v>
+      </c>
+      <c r="E139">
+        <v>460</v>
+      </c>
+      <c r="F139">
+        <v>460</v>
+      </c>
+      <c r="G139">
+        <v>7.5</v>
+      </c>
+      <c r="H139">
+        <v>2180110</v>
+      </c>
+      <c r="I139">
+        <v>69</v>
+      </c>
+      <c r="J139">
+        <v>79</v>
+      </c>
+      <c r="K139" t="s">
+        <v>27</v>
+      </c>
+      <c r="L139" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>12</v>
+      </c>
+      <c r="B140" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140">
+        <v>2021</v>
+      </c>
+      <c r="D140" t="s">
+        <v>32</v>
+      </c>
+      <c r="E140">
+        <v>806</v>
+      </c>
+      <c r="F140">
+        <v>700</v>
+      </c>
+      <c r="G140">
+        <v>7.3</v>
+      </c>
+      <c r="H140">
+        <v>1104173</v>
+      </c>
+      <c r="I140">
+        <v>86</v>
+      </c>
+      <c r="J140">
+        <v>70</v>
+      </c>
+      <c r="K140" t="s">
+        <v>27</v>
+      </c>
+      <c r="L140" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>12</v>
+      </c>
+      <c r="B141" t="s">
+        <v>17</v>
+      </c>
+      <c r="C141">
+        <v>2023</v>
+      </c>
+      <c r="D141" t="s">
+        <v>12</v>
+      </c>
+      <c r="E141">
+        <v>986</v>
+      </c>
+      <c r="F141">
+        <v>319</v>
+      </c>
+      <c r="G141">
+        <v>14.2</v>
+      </c>
+      <c r="H141">
+        <v>1335341</v>
+      </c>
+      <c r="I141">
+        <v>108</v>
+      </c>
+      <c r="J141">
+        <v>92</v>
+      </c>
+      <c r="K141" t="s">
+        <v>15</v>
+      </c>
+      <c r="L141" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>12</v>
+      </c>
+      <c r="B142" t="s">
+        <v>26</v>
+      </c>
+      <c r="C142">
+        <v>2021</v>
+      </c>
+      <c r="D142" t="s">
+        <v>22</v>
+      </c>
+      <c r="E142">
+        <v>869</v>
+      </c>
+      <c r="F142">
+        <v>845</v>
+      </c>
+      <c r="G142">
+        <v>5.2</v>
+      </c>
+      <c r="H142">
+        <v>723052</v>
+      </c>
+      <c r="I142">
+        <v>92</v>
+      </c>
+      <c r="J142">
+        <v>75</v>
+      </c>
+      <c r="K142" t="s">
+        <v>27</v>
+      </c>
+      <c r="L142" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>12</v>
+      </c>
+      <c r="B143" t="s">
+        <v>33</v>
+      </c>
+      <c r="C143">
+        <v>2020</v>
+      </c>
+      <c r="D143" t="s">
+        <v>32</v>
+      </c>
+      <c r="E143">
+        <v>802</v>
+      </c>
+      <c r="F143">
+        <v>634</v>
+      </c>
+      <c r="G143">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="H143">
+        <v>2278111</v>
+      </c>
+      <c r="I143">
+        <v>149</v>
+      </c>
+      <c r="J143">
+        <v>93</v>
+      </c>
+      <c r="K143" t="s">
+        <v>27</v>
+      </c>
+      <c r="L143" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>25</v>
+      </c>
+      <c r="B144" t="s">
+        <v>40</v>
+      </c>
+      <c r="C144">
+        <v>2021</v>
+      </c>
+      <c r="D144" t="s">
+        <v>14</v>
+      </c>
+      <c r="E144">
+        <v>426</v>
+      </c>
+      <c r="F144">
+        <v>158</v>
+      </c>
+      <c r="G144">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="H144">
+        <v>1235304</v>
+      </c>
+      <c r="I144">
+        <v>71</v>
+      </c>
+      <c r="J144">
+        <v>88</v>
+      </c>
+      <c r="K144" t="s">
+        <v>23</v>
+      </c>
+      <c r="L144" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>25</v>
+      </c>
+      <c r="B145" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145">
+        <v>2023</v>
+      </c>
+      <c r="D145" t="s">
+        <v>18</v>
+      </c>
+      <c r="E145">
+        <v>511</v>
+      </c>
+      <c r="F145">
+        <v>484</v>
+      </c>
+      <c r="G145">
+        <v>5.9</v>
+      </c>
+      <c r="H145">
+        <v>1172712</v>
+      </c>
+      <c r="I145">
+        <v>88</v>
+      </c>
+      <c r="J145">
+        <v>70</v>
+      </c>
+      <c r="K145" t="s">
+        <v>27</v>
+      </c>
+      <c r="L145" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>12</v>
+      </c>
+      <c r="B146" t="s">
+        <v>40</v>
+      </c>
+      <c r="C146">
+        <v>2023</v>
+      </c>
+      <c r="D146" t="s">
+        <v>12</v>
+      </c>
+      <c r="E146">
+        <v>872</v>
+      </c>
+      <c r="F146">
+        <v>198</v>
+      </c>
+      <c r="G146">
+        <v>13.2</v>
+      </c>
+      <c r="H146">
+        <v>621867</v>
+      </c>
+      <c r="I146">
+        <v>173</v>
+      </c>
+      <c r="J146">
+        <v>66</v>
+      </c>
+      <c r="K146" t="s">
+        <v>15</v>
+      </c>
+      <c r="L146" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>25</v>
+      </c>
+      <c r="B147" t="s">
+        <v>33</v>
+      </c>
+      <c r="C147">
+        <v>2018</v>
+      </c>
+      <c r="D147" t="s">
+        <v>34</v>
+      </c>
+      <c r="E147">
+        <v>366</v>
+      </c>
+      <c r="F147">
+        <v>207</v>
+      </c>
+      <c r="G147">
+        <v>13.7</v>
+      </c>
+      <c r="H147">
+        <v>1566073</v>
+      </c>
+      <c r="I147">
+        <v>94</v>
+      </c>
+      <c r="J147">
+        <v>99</v>
+      </c>
+      <c r="K147" t="s">
+        <v>15</v>
+      </c>
+      <c r="L147" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>25</v>
+      </c>
+      <c r="B148" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148">
+        <v>2024</v>
+      </c>
+      <c r="D148" t="s">
+        <v>34</v>
+      </c>
+      <c r="E148">
+        <v>422</v>
+      </c>
+      <c r="F148">
+        <v>422</v>
+      </c>
+      <c r="G148">
+        <v>4.8</v>
+      </c>
+      <c r="H148">
+        <v>1559539</v>
+      </c>
+      <c r="I148">
+        <v>170</v>
+      </c>
+      <c r="J148">
+        <v>82</v>
+      </c>
+      <c r="K148" t="s">
+        <v>19</v>
+      </c>
+      <c r="L148" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>12</v>
+      </c>
+      <c r="B149" t="s">
+        <v>40</v>
+      </c>
+      <c r="C149">
+        <v>2023</v>
+      </c>
+      <c r="D149" t="s">
+        <v>32</v>
+      </c>
+      <c r="E149">
+        <v>375</v>
+      </c>
+      <c r="F149">
+        <v>52</v>
+      </c>
+      <c r="G149">
+        <v>8.5</v>
+      </c>
+      <c r="H149">
+        <v>663310</v>
+      </c>
+      <c r="I149">
+        <v>63</v>
+      </c>
+      <c r="J149">
+        <v>62</v>
+      </c>
+      <c r="K149" t="s">
+        <v>27</v>
+      </c>
+      <c r="L149" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>12</v>
+      </c>
+      <c r="B150" t="s">
+        <v>26</v>
+      </c>
+      <c r="C150">
+        <v>2020</v>
+      </c>
+      <c r="D150" t="s">
+        <v>29</v>
+      </c>
+      <c r="E150">
+        <v>406</v>
+      </c>
+      <c r="F150">
+        <v>406</v>
+      </c>
+      <c r="G150">
+        <v>7.6</v>
+      </c>
+      <c r="H150">
+        <v>590687</v>
+      </c>
+      <c r="I150">
+        <v>121</v>
+      </c>
+      <c r="J150">
+        <v>84</v>
+      </c>
+      <c r="K150" t="s">
+        <v>27</v>
+      </c>
+      <c r="L150" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>25</v>
+      </c>
+      <c r="B151" t="s">
+        <v>26</v>
+      </c>
+      <c r="C151">
+        <v>2018</v>
+      </c>
+      <c r="D151" t="s">
+        <v>22</v>
+      </c>
+      <c r="E151">
+        <v>826</v>
+      </c>
+      <c r="F151">
+        <v>636</v>
+      </c>
+      <c r="G151">
+        <v>3.2</v>
+      </c>
+      <c r="H151">
+        <v>2341623</v>
+      </c>
+      <c r="I151">
+        <v>123</v>
+      </c>
+      <c r="J151">
+        <v>76</v>
+      </c>
+      <c r="K151" t="s">
+        <v>19</v>
+      </c>
+      <c r="L151" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27651,8 +33438,8 @@
     <col min="19" max="19" width="5.42578125" customWidth="1"/>
     <col min="20" max="20" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="28.28515625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="31.28515625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -28705,7 +34492,7 @@
         <v>0.93158153904268515</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -28765,7 +34552,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -28830,12 +34617,11 @@
       <c r="W18" t="s">
         <v>42</v>
       </c>
-      <c r="X18">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","East Midlands")</f>
-        <v>1031</v>
+      <c r="X18" s="14" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -28900,12 +34686,12 @@
       <c r="W19" s="13">
         <v>1031</v>
       </c>
-      <c r="X19">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","East of England")</f>
-        <v>2067</v>
+      <c r="X19" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","East Midlands")</f>
+        <v>1031</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -28970,12 +34756,12 @@
       <c r="W20">
         <v>2067</v>
       </c>
-      <c r="X20">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","London")</f>
-        <v>1060</v>
+      <c r="X20" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","East of England")</f>
+        <v>2067</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -29040,12 +34826,12 @@
       <c r="W21">
         <v>1060</v>
       </c>
-      <c r="X21">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","North East")</f>
-        <v>1592</v>
+      <c r="X21" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","London")</f>
+        <v>1060</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -29110,12 +34896,12 @@
       <c r="W22">
         <v>1592</v>
       </c>
-      <c r="X22">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","North West")</f>
-        <v>2049</v>
+      <c r="X22" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","North East")</f>
+        <v>1592</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -29180,12 +34966,12 @@
       <c r="W23">
         <v>2049</v>
       </c>
-      <c r="X23">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Northern Ireland")</f>
-        <v>857</v>
+      <c r="X23" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","North West")</f>
+        <v>2049</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -29250,12 +35036,12 @@
       <c r="W24">
         <v>857</v>
       </c>
-      <c r="X24">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Scotland")</f>
-        <v>1925</v>
+      <c r="X24" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Northern Ireland")</f>
+        <v>857</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -29320,12 +35106,12 @@
       <c r="W25">
         <v>1925</v>
       </c>
-      <c r="X25">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","South East")</f>
-        <v>1480</v>
+      <c r="X25" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Scotland")</f>
+        <v>1925</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -29390,12 +35176,12 @@
       <c r="W26">
         <v>1480</v>
       </c>
-      <c r="X26">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","South West")</f>
-        <v>1382</v>
+      <c r="X26" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","South East")</f>
+        <v>1480</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -29460,12 +35246,12 @@
       <c r="W27">
         <v>1382</v>
       </c>
-      <c r="X27">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Wales")</f>
-        <v>1796</v>
+      <c r="X27" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","South West")</f>
+        <v>1382</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -29530,12 +35316,12 @@
       <c r="W28">
         <v>1796</v>
       </c>
-      <c r="X28">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","West Midlands")</f>
-        <v>1756</v>
+      <c r="X28" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Wales")</f>
+        <v>1796</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -29588,12 +35374,12 @@
       <c r="W29">
         <v>1756</v>
       </c>
-      <c r="X29">
-        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Yorkshire and the Humber")</f>
-        <v>1234</v>
+      <c r="X29" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","West Midlands")</f>
+        <v>1756</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -29646,8 +35432,12 @@
       <c r="W30">
         <v>1234</v>
       </c>
+      <c r="X30" s="15">
+        <f>GETPIVOTDATA("Staff Count",$T$17,"Region","Yorkshire and the Humber")</f>
+        <v>1234</v>
+      </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -35214,7 +41004,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB22A8D6-E718-40CE-A5FF-5713FD1BC5A0}">
   <dimension ref="A1:AN29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -35223,384 +41013,384 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-      <c r="AI1" s="14"/>
-      <c r="AJ1" s="14"/>
-      <c r="AK1" s="14"/>
-      <c r="AL1" s="14"/>
-      <c r="AM1" s="14"/>
-      <c r="AN1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16"/>
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="16"/>
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="16"/>
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16"/>
     </row>
     <row r="2" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="14"/>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="14"/>
-      <c r="AH2" s="14"/>
-      <c r="AI2" s="14"/>
-      <c r="AJ2" s="14"/>
-      <c r="AK2" s="14"/>
-      <c r="AL2" s="14"/>
-      <c r="AM2" s="14"/>
-      <c r="AN2" s="14"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
-      <c r="AJ3" s="14"/>
-      <c r="AK3" s="14"/>
-      <c r="AL3" s="14"/>
-      <c r="AM3" s="14"/>
-      <c r="AN3" s="14"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
+      <c r="AJ3" s="16"/>
+      <c r="AK3" s="16"/>
+      <c r="AL3" s="16"/>
+      <c r="AM3" s="16"/>
+      <c r="AN3" s="16"/>
     </row>
     <row r="4" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="14"/>
-      <c r="AF4" s="14"/>
-      <c r="AG4" s="14"/>
-      <c r="AH4" s="14"/>
-      <c r="AI4" s="14"/>
-      <c r="AJ4" s="14"/>
-      <c r="AK4" s="14"/>
-      <c r="AL4" s="14"/>
-      <c r="AM4" s="14"/>
-      <c r="AN4" s="14"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="16"/>
+      <c r="AA4" s="16"/>
+      <c r="AB4" s="16"/>
+      <c r="AC4" s="16"/>
+      <c r="AD4" s="16"/>
+      <c r="AE4" s="16"/>
+      <c r="AF4" s="16"/>
+      <c r="AG4" s="16"/>
+      <c r="AH4" s="16"/>
+      <c r="AI4" s="16"/>
+      <c r="AJ4" s="16"/>
+      <c r="AK4" s="16"/>
+      <c r="AL4" s="16"/>
+      <c r="AM4" s="16"/>
+      <c r="AN4" s="16"/>
     </row>
     <row r="5" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="14"/>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="14"/>
-      <c r="AF5" s="14"/>
-      <c r="AG5" s="14"/>
-      <c r="AH5" s="14"/>
-      <c r="AI5" s="14"/>
-      <c r="AJ5" s="14"/>
-      <c r="AK5" s="14"/>
-      <c r="AL5" s="14"/>
-      <c r="AM5" s="14"/>
-      <c r="AN5" s="14"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AC5" s="16"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="16"/>
+      <c r="AF5" s="16"/>
+      <c r="AG5" s="16"/>
+      <c r="AH5" s="16"/>
+      <c r="AI5" s="16"/>
+      <c r="AJ5" s="16"/>
+      <c r="AK5" s="16"/>
+      <c r="AL5" s="16"/>
+      <c r="AM5" s="16"/>
+      <c r="AN5" s="16"/>
     </row>
     <row r="6" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="14"/>
-      <c r="AD6" s="14"/>
-      <c r="AE6" s="14"/>
-      <c r="AF6" s="14"/>
-      <c r="AG6" s="14"/>
-      <c r="AH6" s="14"/>
-      <c r="AI6" s="14"/>
-      <c r="AJ6" s="14"/>
-      <c r="AK6" s="14"/>
-      <c r="AL6" s="14"/>
-      <c r="AM6" s="14"/>
-      <c r="AN6" s="14"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="16"/>
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="16"/>
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="16"/>
+      <c r="AA6" s="16"/>
+      <c r="AB6" s="16"/>
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="16"/>
+      <c r="AF6" s="16"/>
+      <c r="AG6" s="16"/>
+      <c r="AH6" s="16"/>
+      <c r="AI6" s="16"/>
+      <c r="AJ6" s="16"/>
+      <c r="AK6" s="16"/>
+      <c r="AL6" s="16"/>
+      <c r="AM6" s="16"/>
+      <c r="AN6" s="16"/>
     </row>
     <row r="7" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="14"/>
-      <c r="AD7" s="14"/>
-      <c r="AE7" s="14"/>
-      <c r="AF7" s="14"/>
-      <c r="AG7" s="14"/>
-      <c r="AH7" s="14"/>
-      <c r="AI7" s="14"/>
-      <c r="AJ7" s="14"/>
-      <c r="AK7" s="14"/>
-      <c r="AL7" s="14"/>
-      <c r="AM7" s="14"/>
-      <c r="AN7" s="14"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="16"/>
+      <c r="U7" s="16"/>
+      <c r="V7" s="16"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="16"/>
+      <c r="AA7" s="16"/>
+      <c r="AB7" s="16"/>
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="16"/>
+      <c r="AF7" s="16"/>
+      <c r="AG7" s="16"/>
+      <c r="AH7" s="16"/>
+      <c r="AI7" s="16"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16"/>
+      <c r="AL7" s="16"/>
+      <c r="AM7" s="16"/>
+      <c r="AN7" s="16"/>
     </row>
     <row r="8" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="14"/>
-      <c r="AC8" s="14"/>
-      <c r="AD8" s="14"/>
-      <c r="AE8" s="14"/>
-      <c r="AF8" s="14"/>
-      <c r="AG8" s="14"/>
-      <c r="AH8" s="14"/>
-      <c r="AI8" s="14"/>
-      <c r="AJ8" s="14"/>
-      <c r="AK8" s="14"/>
-      <c r="AL8" s="14"/>
-      <c r="AM8" s="14"/>
-      <c r="AN8" s="14"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="16"/>
+      <c r="AI8" s="16"/>
+      <c r="AJ8" s="16"/>
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="16"/>
+      <c r="AM8" s="16"/>
+      <c r="AN8" s="16"/>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
-      <c r="AD9" s="14"/>
-      <c r="AE9" s="14"/>
-      <c r="AF9" s="14"/>
-      <c r="AG9" s="14"/>
-      <c r="AH9" s="14"/>
-      <c r="AI9" s="14"/>
-      <c r="AJ9" s="14"/>
-      <c r="AK9" s="14"/>
-      <c r="AL9" s="14"/>
-      <c r="AM9" s="14"/>
-      <c r="AN9" s="14"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="16"/>
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="16"/>
+      <c r="AM9" s="16"/>
+      <c r="AN9" s="16"/>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
@@ -35623,7 +41413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3CC2DFB-5CAB-4788-8179-B254F833884D}">
   <dimension ref="I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -35641,15 +41431,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003B13CFFDAAE59C4CA678E7EE4E73178D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e05d12ad55831ca1d94ab0d6bf4c33ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f7ad296a-57ff-428c-b4cb-07edbf36982d" xmlns:ns3="2d161a28-3536-4ba6-9ad5-e5ce0dbbadc5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="accd58e9f676c36d920d788803336cd6" ns2:_="" ns3:_="">
     <xsd:import namespace="f7ad296a-57ff-428c-b4cb-07edbf36982d"/>
@@ -35844,7 +41625,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="f7ad296a-57ff-428c-b4cb-07edbf36982d">
@@ -35855,15 +41636,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1632C448-2796-4273-B186-9F60F8DD736F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72BB855-D9E2-418E-8D59-E846EEFC1235}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -35882,7 +41664,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD253A9A-6DC7-4FA1-AF78-9A17C6B0F5FE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -35897,4 +41679,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1632C448-2796-4273-B186-9F60F8DD736F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>